--- a/ADBE.xlsx
+++ b/ADBE.xlsx
@@ -48,15 +48,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>22</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -81,15 +81,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>24</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>28</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -114,15 +114,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>18</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>12</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>19</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>22</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -148,15 +148,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>18</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>18</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>19</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>22</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -181,15 +181,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>19</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>18</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>20</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>22</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -215,15 +215,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>20</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>18</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>21</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>22</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -248,15 +248,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>20</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>54</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>21</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>58</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -281,15 +281,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>31</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>36</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>32</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>40</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -314,15 +314,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>33</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>34</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>7</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -347,15 +347,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>33</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>18</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>34</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>22</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -380,15 +380,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>33</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>54</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>34</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>58</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -413,15 +413,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>34</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>35</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>7</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -446,15 +446,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>35</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>36</xdr:col>
-                <xdr:colOff>19</xdr:colOff>
+                <xdr:colOff>8</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>7</xdr:rowOff>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -467,7 +467,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="282">
   <si>
     <t xml:space="preserve">Adobe Inc.</t>
   </si>
@@ -1006,13 +1006,22 @@
     <t xml:space="preserve">Shares</t>
   </si>
   <si>
+    <t xml:space="preserve">Gordon Growth Model</t>
+  </si>
+  <si>
     <t xml:space="preserve">Revenue q/q</t>
   </si>
   <si>
     <t xml:space="preserve">Terminal</t>
   </si>
   <si>
+    <t xml:space="preserve">Payout Ratio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sustained Growth</t>
   </si>
   <si>
     <t xml:space="preserve">Op Margin</t>
@@ -1021,10 +1030,16 @@
     <t xml:space="preserve">ROIC</t>
   </si>
   <si>
+    <t xml:space="preserve">Equity Value</t>
+  </si>
+  <si>
     <t xml:space="preserve">NI Margin</t>
   </si>
   <si>
     <t xml:space="preserve">NPV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Just. P/E</t>
   </si>
   <si>
     <t xml:space="preserve">Tax Rate</t>
@@ -1036,7 +1051,13 @@
     <t xml:space="preserve">Diff</t>
   </si>
   <si>
+    <t xml:space="preserve">Dividend Payout</t>
+  </si>
+  <si>
     <t xml:space="preserve">Incr. Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt-to-EBITDA</t>
   </si>
   <si>
     <t xml:space="preserve">Subscription % Rev</t>
@@ -1048,7 +1069,13 @@
     <t xml:space="preserve">Services % Rev</t>
   </si>
   <si>
+    <t xml:space="preserve">Debt (-)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ROA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash (+)</t>
   </si>
   <si>
     <t xml:space="preserve">ROE</t>
@@ -1210,6 +1237,21 @@
     <t xml:space="preserve">CCC</t>
   </si>
   <si>
+    <t xml:space="preserve">Share Issuance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y/Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share Repurchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total SH Return</t>
+  </si>
+  <si>
     <t xml:space="preserve">ISIN</t>
   </si>
   <si>
@@ -1292,7 +1334,7 @@
     <numFmt numFmtId="175" formatCode="0.00%;\(0.00%\)"/>
     <numFmt numFmtId="176" formatCode="@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1391,6 +1433,15 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1434,7 +1485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1484,6 +1535,13 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1510,7 +1568,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1663,6 +1721,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1723,6 +1785,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="175" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1747,15 +1817,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1779,8 +1849,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2020,11 +2094,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="88121073"/>
-        <c:axId val="60400669"/>
+        <c:axId val="97608476"/>
+        <c:axId val="77484863"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="88121073"/>
+        <c:axId val="97608476"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2057,7 +2131,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60400669"/>
+        <c:crossAx val="77484863"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2065,7 +2139,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60400669"/>
+        <c:axId val="77484863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2107,7 +2181,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88121073"/>
+        <c:crossAx val="97608476"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2532,11 +2606,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="17382453"/>
-        <c:axId val="57155327"/>
+        <c:axId val="48431707"/>
+        <c:axId val="42949808"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17382453"/>
+        <c:axId val="48431707"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2569,7 +2643,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57155327"/>
+        <c:crossAx val="42949808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2577,7 +2651,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57155327"/>
+        <c:axId val="42949808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +2693,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17382453"/>
+        <c:crossAx val="48431707"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2897,11 +2971,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="61228423"/>
-        <c:axId val="98208795"/>
+        <c:axId val="66888992"/>
+        <c:axId val="36883099"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61228423"/>
+        <c:axId val="66888992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2934,7 +3008,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98208795"/>
+        <c:crossAx val="36883099"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2942,7 +3016,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98208795"/>
+        <c:axId val="36883099"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2984,7 +3058,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61228423"/>
+        <c:crossAx val="66888992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3677,8 +3751,8 @@
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>119520</xdr:colOff>
-      <xdr:row>169</xdr:row>
-      <xdr:rowOff>35280</xdr:rowOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>106200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3711,15 +3785,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>70200</xdr:colOff>
+      <xdr:colOff>70560</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>104040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>70920</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>159840</xdr:rowOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>73800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3728,8 +3802,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="16255800" y="104040"/>
-          <a:ext cx="720" cy="15523200"/>
+          <a:off x="16256160" y="104040"/>
+          <a:ext cx="360" cy="26244720"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3752,15 +3826,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>528120</xdr:colOff>
-      <xdr:row>158</xdr:row>
-      <xdr:rowOff>90720</xdr:rowOff>
+      <xdr:colOff>483120</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>24840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>597600</xdr:colOff>
-      <xdr:row>178</xdr:row>
-      <xdr:rowOff>78480</xdr:rowOff>
+      <xdr:colOff>551880</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>11880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3768,8 +3842,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="23216040" y="24811200"/>
-        <a:ext cx="5758920" cy="3238920"/>
+        <a:off x="23171040" y="26137440"/>
+        <a:ext cx="5758200" cy="3238200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3782,15 +3856,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>35</xdr:col>
-      <xdr:colOff>635400</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>55440</xdr:rowOff>
+      <xdr:colOff>620280</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>136800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>704520</xdr:colOff>
-      <xdr:row>177</xdr:row>
-      <xdr:rowOff>43200</xdr:rowOff>
+      <xdr:colOff>688680</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>19440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3798,8 +3872,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="29825640" y="24613560"/>
-        <a:ext cx="5758920" cy="3238920"/>
+        <a:off x="29810520" y="25819920"/>
+        <a:ext cx="5758200" cy="3238200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3812,15 +3886,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>79920</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>28080</xdr:rowOff>
+      <xdr:colOff>44640</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>146880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>149040</xdr:colOff>
-      <xdr:row>179</xdr:row>
-      <xdr:rowOff>15840</xdr:rowOff>
+      <xdr:colOff>113040</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>133920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3828,8 +3902,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10575720" y="24911280"/>
-        <a:ext cx="5758920" cy="3238920"/>
+        <a:off x="10540440" y="27397440"/>
+        <a:ext cx="5758200" cy="3238200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4087,8 +4161,8 @@
         <v>12</v>
       </c>
       <c r="E11" s="10" t="n">
-        <f aca="false">+(F4/(F4+F5))*B10+(F5/(F4+F5))*B11*(1-Model!AF68)</f>
-        <v>0.114884329162756</v>
+        <f aca="false">+(F3/(F3+F5))*B10+(F5/(F3+F5))*B11*(1-Model!AF68)</f>
+        <v>0.12600247770003</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4827,7 +4901,9 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="22.06"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="3" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="48" min="2" style="3" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="3" width="15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="50" style="3" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16143,10 +16219,14 @@
       <c r="AO63" s="1"/>
       <c r="AR63" s="1"/>
       <c r="AS63" s="1"/>
+      <c r="AW63" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="AX63" s="38"/>
     </row>
-    <row r="64" s="40" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="n">
@@ -16249,15 +16329,20 @@
       <c r="AQ64" s="16"/>
       <c r="AR64" s="1"/>
       <c r="AS64" s="1"/>
-      <c r="AT64" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="AU64" s="39" t="n">
+      <c r="AT64" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="AU64" s="40" t="n">
         <v>-0.01</v>
       </c>
       <c r="AV64" s="31"/>
-      <c r="AW64" s="31"/>
-      <c r="AX64" s="31"/>
+      <c r="AW64" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="AX64" s="34" t="n">
+        <f aca="false">+SUM(P166:S166)/SUM(P57:S57)</f>
+        <v>1.21510582376539</v>
+      </c>
       <c r="AY64" s="31"/>
       <c r="AZ64" s="31"/>
       <c r="BA64" s="31"/>
@@ -16339,7 +16424,7 @@
       <c r="DY64" s="31"/>
       <c r="DZ64" s="31"/>
     </row>
-    <row r="65" s="40" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="16" t="s">
         <v>163</v>
       </c>
@@ -16498,16 +16583,18 @@
       </c>
       <c r="AR65" s="1"/>
       <c r="AS65" s="1"/>
-      <c r="AT65" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="AU65" s="42" t="n">
+      <c r="AT65" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="AU65" s="43" t="n">
         <f aca="false">+Main!E11</f>
-        <v>0.114884329162756</v>
+        <v>0.12600247770003</v>
       </c>
       <c r="AV65" s="16"/>
-      <c r="AW65" s="16"/>
-      <c r="AX65" s="16"/>
+      <c r="AW65" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="AX65" s="34"/>
       <c r="AY65" s="16"/>
       <c r="AZ65" s="16"/>
       <c r="BA65" s="16"/>
@@ -16591,7 +16678,7 @@
     </row>
     <row r="66" s="25" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B66" s="16" t="n">
         <f aca="false">+B45/B23</f>
@@ -16748,15 +16835,17 @@
       </c>
       <c r="AR66" s="1"/>
       <c r="AS66" s="1"/>
-      <c r="AT66" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="AU66" s="44" t="n">
+      <c r="AT66" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="AU66" s="45" t="n">
         <v>0.02</v>
       </c>
       <c r="AV66" s="16"/>
-      <c r="AW66" s="16"/>
-      <c r="AX66" s="16"/>
+      <c r="AW66" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="AX66" s="34"/>
       <c r="AY66" s="16"/>
       <c r="AZ66" s="16"/>
       <c r="BA66" s="16"/>
@@ -16838,9 +16927,9 @@
       <c r="DY66" s="16"/>
       <c r="DZ66" s="16"/>
     </row>
-    <row r="67" s="40" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B67" s="16" t="n">
         <f aca="false">+B57/B23</f>
@@ -16997,16 +17086,18 @@
       </c>
       <c r="AR67" s="1"/>
       <c r="AS67" s="1"/>
-      <c r="AT67" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="AU67" s="46" t="n">
+      <c r="AT67" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="AU67" s="47" t="n">
         <f aca="false">NPV(AU65,AG57:DZ57)</f>
-        <v>153093.643491881</v>
+        <v>136869.55014887</v>
       </c>
       <c r="AV67" s="16"/>
-      <c r="AW67" s="16"/>
-      <c r="AX67" s="16"/>
+      <c r="AW67" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="AX67" s="34"/>
       <c r="AY67" s="16"/>
       <c r="AZ67" s="16"/>
       <c r="BA67" s="16"/>
@@ -17090,7 +17181,7 @@
     </row>
     <row r="68" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="16" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B68" s="16" t="n">
         <f aca="false">+B55/B53</f>
@@ -17247,16 +17338,16 @@
       </c>
       <c r="AR68" s="1"/>
       <c r="AS68" s="1"/>
-      <c r="AT68" s="43" t="s">
+      <c r="AT68" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="AU68" s="47" t="n">
+      <c r="AU68" s="48" t="n">
         <f aca="false">+AU67/Main!F1</f>
-        <v>668.531194287688</v>
+        <v>597.683625104238</v>
       </c>
       <c r="AV68" s="16"/>
-      <c r="AW68" s="16"/>
-      <c r="AX68" s="16"/>
+      <c r="AW68" s="34"/>
+      <c r="AX68" s="34"/>
       <c r="AY68" s="16"/>
       <c r="AZ68" s="16"/>
       <c r="BA68" s="16"/>
@@ -17340,7 +17431,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="31" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
@@ -17485,16 +17576,20 @@
       </c>
       <c r="AR69" s="1"/>
       <c r="AS69" s="1"/>
-      <c r="AT69" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="AU69" s="49" t="n">
+      <c r="AT69" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="AU69" s="50" t="n">
         <f aca="false">+AU68/Main!F1-1</f>
-        <v>1.91935019339602</v>
+        <v>1.60997216202724</v>
       </c>
       <c r="AV69" s="16"/>
-      <c r="AW69" s="16"/>
-      <c r="AX69" s="16"/>
+      <c r="AW69" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="AX69" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="AY69" s="16"/>
       <c r="AZ69" s="16"/>
       <c r="BA69" s="16"/>
@@ -17578,7 +17673,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -17717,8 +17812,13 @@
       <c r="AT70" s="16"/>
       <c r="AU70" s="16"/>
       <c r="AV70" s="16"/>
-      <c r="AW70" s="16"/>
-      <c r="AX70" s="16"/>
+      <c r="AW70" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX70" s="3" t="n">
+        <f aca="false">+(-S92+S109+S110)</f>
+        <v>1726</v>
+      </c>
       <c r="AY70" s="16"/>
       <c r="AZ70" s="16"/>
       <c r="BA70" s="16"/>
@@ -17934,7 +18034,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B72" s="16" t="n">
         <f aca="false">+B17/B$23</f>
@@ -18146,7 +18246,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B73" s="16" t="n">
         <f aca="false">+B19/B$23</f>
@@ -18358,7 +18458,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B74" s="16" t="n">
         <f aca="false">+B21/B$23</f>
@@ -18617,8 +18717,13 @@
       <c r="AT75" s="34"/>
       <c r="AU75" s="34"/>
       <c r="AV75" s="34"/>
-      <c r="AW75" s="34"/>
-      <c r="AX75" s="34"/>
+      <c r="AW75" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX75" s="3" t="n">
+        <f aca="false">+AU78</f>
+        <v>126091.329193723</v>
+      </c>
       <c r="AY75" s="34"/>
       <c r="AZ75" s="34"/>
       <c r="BA75" s="34"/>
@@ -18746,15 +18851,20 @@
       <c r="AQ76" s="35"/>
       <c r="AR76" s="1"/>
       <c r="AS76" s="1"/>
-      <c r="AT76" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="AU76" s="51" t="n">
+      <c r="AT76" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="AU76" s="52" t="n">
         <v>-0.01</v>
       </c>
       <c r="AV76" s="34"/>
-      <c r="AW76" s="34"/>
-      <c r="AX76" s="34"/>
+      <c r="AW76" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="AX76" s="3" t="n">
+        <f aca="false">+Main!F5</f>
+        <v>6645</v>
+      </c>
       <c r="AY76" s="34"/>
       <c r="AZ76" s="34"/>
       <c r="BA76" s="34"/>
@@ -18838,7 +18948,7 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="16" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16" t="n">
@@ -18950,16 +19060,21 @@
       <c r="AQ77" s="16"/>
       <c r="AR77" s="1"/>
       <c r="AS77" s="1"/>
-      <c r="AT77" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="AU77" s="44" t="n">
+      <c r="AT77" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="AU77" s="45" t="n">
         <f aca="false">+Main!E11</f>
-        <v>0.114884329162756</v>
+        <v>0.12600247770003</v>
       </c>
       <c r="AV77" s="35"/>
-      <c r="AW77" s="35"/>
-      <c r="AX77" s="35"/>
+      <c r="AW77" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="AX77" s="55" t="n">
+        <f aca="false">+Main!F4</f>
+        <v>5626</v>
+      </c>
       <c r="AY77" s="35"/>
       <c r="AZ77" s="35"/>
       <c r="BA77" s="35"/>
@@ -19043,7 +19158,7 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="16" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B78" s="16"/>
       <c r="C78" s="16" t="n">
@@ -19155,16 +19270,21 @@
       <c r="AQ78" s="16"/>
       <c r="AR78" s="19"/>
       <c r="AS78" s="19"/>
-      <c r="AT78" s="53" t="s">
+      <c r="AT78" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AU78" s="54" t="n">
+      <c r="AU78" s="57" t="n">
         <f aca="false">+NPV(AU77,AG87:AP87,AQ87+AU79)</f>
-        <v>140413.634007275</v>
+        <v>126091.329193723</v>
       </c>
       <c r="AV78" s="35"/>
-      <c r="AW78" s="35"/>
-      <c r="AX78" s="35"/>
+      <c r="AW78" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="AX78" s="3" t="n">
+        <f aca="false">+AX75-AX76+AX77</f>
+        <v>125072.329193723</v>
+      </c>
       <c r="AY78" s="35"/>
       <c r="AZ78" s="35"/>
       <c r="BA78" s="35"/>
@@ -19248,7 +19368,7 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="16" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B79" s="16"/>
       <c r="C79" s="16" t="n">
@@ -19360,16 +19480,21 @@
       <c r="AQ79" s="16"/>
       <c r="AR79" s="19"/>
       <c r="AS79" s="19"/>
-      <c r="AT79" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="AU79" s="55" t="n">
+      <c r="AT79" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="AU79" s="58" t="n">
         <f aca="false">+AQ87*(1+AU76)/(AU77-AU76)</f>
-        <v>175780.412670864</v>
+        <v>161410.433747918</v>
       </c>
       <c r="AV79" s="34"/>
-      <c r="AW79" s="34"/>
-      <c r="AX79" s="34"/>
+      <c r="AW79" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="AX79" s="55" t="n">
+        <f aca="false">+Main!F2</f>
+        <v>397.5</v>
+      </c>
       <c r="AY79" s="34"/>
       <c r="AZ79" s="34"/>
       <c r="BA79" s="34"/>
@@ -19452,129 +19577,134 @@
       <c r="DZ79" s="34"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="56" t="s">
-        <v>197</v>
-      </c>
-      <c r="B80" s="56"/>
-      <c r="C80" s="56" t="n">
+      <c r="A80" s="59" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" s="59"/>
+      <c r="C80" s="59" t="n">
         <f aca="false">+AVERAGE(B115:C115)/AVERAGE(B122:C122)</f>
         <v>0.884102340814656</v>
       </c>
-      <c r="D80" s="56" t="n">
+      <c r="D80" s="59" t="n">
         <f aca="false">+AVERAGE(C115:D115)/AVERAGE(C122:D122)</f>
         <v>0.871455521838377</v>
       </c>
-      <c r="E80" s="56" t="n">
+      <c r="E80" s="59" t="n">
         <f aca="false">+AVERAGE(D115:E115)/AVERAGE(D122:E122)</f>
         <v>0.896628308870987</v>
       </c>
-      <c r="F80" s="56" t="n">
+      <c r="F80" s="59" t="n">
         <f aca="false">+AVERAGE(E115:F115)/AVERAGE(E122:F122)</f>
         <v>0.933342114898262</v>
       </c>
-      <c r="G80" s="56" t="n">
+      <c r="G80" s="59" t="n">
         <f aca="false">+AVERAGE(F115:G115)/AVERAGE(F122:G122)</f>
         <v>0.903968824810016</v>
       </c>
-      <c r="H80" s="56" t="n">
+      <c r="H80" s="59" t="n">
         <f aca="false">+AVERAGE(G115:H115)/AVERAGE(G122:H122)</f>
         <v>0.859564949318074</v>
       </c>
-      <c r="I80" s="56" t="n">
+      <c r="I80" s="59" t="n">
         <f aca="false">+AVERAGE(H115:I115)/AVERAGE(H122:I122)</f>
         <v>0.822931046574039</v>
       </c>
-      <c r="J80" s="56" t="n">
+      <c r="J80" s="59" t="n">
         <f aca="false">+AVERAGE(I115:J115)/AVERAGE(I122:J122)</f>
         <v>0.830342344288713</v>
       </c>
-      <c r="K80" s="56" t="n">
+      <c r="K80" s="59" t="n">
         <f aca="false">+AVERAGE(J115:K115)/AVERAGE(J122:K122)</f>
         <v>0.994985380902562</v>
       </c>
-      <c r="L80" s="56" t="n">
+      <c r="L80" s="59" t="n">
         <f aca="false">+AVERAGE(K115:L115)/AVERAGE(K122:L122)</f>
         <v>1.09636236382236</v>
       </c>
-      <c r="M80" s="56" t="n">
+      <c r="M80" s="59" t="n">
         <f aca="false">+AVERAGE(L115:M115)/AVERAGE(L122:M122)</f>
         <v>1.09636155017009</v>
       </c>
-      <c r="N80" s="56" t="n">
+      <c r="N80" s="59" t="n">
         <f aca="false">+AVERAGE(M115:N115)/AVERAGE(M122:N122)</f>
         <v>1.21271169626724</v>
       </c>
-      <c r="O80" s="56" t="n">
+      <c r="O80" s="59" t="n">
         <f aca="false">+AVERAGE(N115:O115)/AVERAGE(N122:O122)</f>
         <v>1.36575502476633</v>
       </c>
-      <c r="P80" s="56" t="n">
+      <c r="P80" s="59" t="n">
         <f aca="false">+AVERAGE(O115:P115)/AVERAGE(O122:P122)</f>
         <v>1.44903809093363</v>
       </c>
-      <c r="Q80" s="56" t="n">
+      <c r="Q80" s="59" t="n">
         <f aca="false">+AVERAGE(P115:Q115)/AVERAGE(P122:Q122)</f>
         <v>1.49009574552315</v>
       </c>
-      <c r="R80" s="56" t="n">
+      <c r="R80" s="59" t="n">
         <f aca="false">+AVERAGE(Q115:R115)/AVERAGE(Q122:R122)</f>
         <v>1.56769518897396</v>
       </c>
-      <c r="S80" s="56" t="n">
+      <c r="S80" s="59" t="n">
         <f aca="false">+AVERAGE(R115:S115)/AVERAGE(R122:S122)</f>
         <v>1.59848040279216</v>
       </c>
-      <c r="T80" s="56"/>
-      <c r="U80" s="56"/>
-      <c r="V80" s="56"/>
-      <c r="W80" s="56"/>
-      <c r="X80" s="56"/>
-      <c r="Y80" s="56"/>
-      <c r="Z80" s="56"/>
-      <c r="AA80" s="56"/>
-      <c r="AB80" s="56" t="n">
+      <c r="T80" s="59"/>
+      <c r="U80" s="59"/>
+      <c r="V80" s="59"/>
+      <c r="W80" s="59"/>
+      <c r="X80" s="59"/>
+      <c r="Y80" s="59"/>
+      <c r="Z80" s="59"/>
+      <c r="AA80" s="59"/>
+      <c r="AB80" s="59" t="n">
         <f aca="false">+AVERAGE(AA115:AB115)/AVERAGE(AA122:AB122)</f>
         <v>0.836186183119287</v>
       </c>
-      <c r="AC80" s="56" t="n">
+      <c r="AC80" s="59" t="n">
         <f aca="false">+AVERAGE(AB115:AC115)/AVERAGE(AB122:AC122)</f>
         <v>0.885961302264016</v>
       </c>
-      <c r="AD80" s="56" t="n">
+      <c r="AD80" s="59" t="n">
         <f aca="false">+AVERAGE(AC115:AD115)/AVERAGE(AC122:AD122)</f>
         <v>0.862808784276882</v>
       </c>
-      <c r="AE80" s="56" t="n">
+      <c r="AE80" s="59" t="n">
         <f aca="false">+AVERAGE(AD115:AE115)/AVERAGE(AD122:AE122)</f>
         <v>0.959612339828746</v>
       </c>
-      <c r="AF80" s="56" t="n">
+      <c r="AF80" s="59" t="n">
         <f aca="false">+AVERAGE(AE115:AF115)/AVERAGE(AE122:AF122)</f>
         <v>1.3214482288368</v>
       </c>
-      <c r="AG80" s="56"/>
-      <c r="AH80" s="56"/>
-      <c r="AI80" s="56"/>
-      <c r="AJ80" s="56"/>
-      <c r="AK80" s="56"/>
-      <c r="AL80" s="56"/>
-      <c r="AM80" s="56"/>
-      <c r="AN80" s="56"/>
-      <c r="AO80" s="56"/>
-      <c r="AP80" s="56"/>
-      <c r="AQ80" s="56"/>
+      <c r="AG80" s="59"/>
+      <c r="AH80" s="59"/>
+      <c r="AI80" s="59"/>
+      <c r="AJ80" s="59"/>
+      <c r="AK80" s="59"/>
+      <c r="AL80" s="59"/>
+      <c r="AM80" s="59"/>
+      <c r="AN80" s="59"/>
+      <c r="AO80" s="59"/>
+      <c r="AP80" s="59"/>
+      <c r="AQ80" s="59"/>
       <c r="AR80" s="15"/>
       <c r="AS80" s="15"/>
-      <c r="AT80" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="AU80" s="58" t="n">
+      <c r="AT80" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="AU80" s="61" t="n">
         <f aca="false">+AU78/Main!F6-1</f>
-        <v>0.525464129622256</v>
+        <v>0.369865548323109</v>
       </c>
       <c r="AV80" s="34"/>
-      <c r="AW80" s="34"/>
-      <c r="AX80" s="34"/>
+      <c r="AW80" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX80" s="3" t="n">
+        <f aca="false">+AX78/AX79</f>
+        <v>314.647369040813</v>
+      </c>
       <c r="AY80" s="34"/>
       <c r="AZ80" s="34"/>
       <c r="BA80" s="34"/>
@@ -19658,7 +19788,7 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="16" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16" t="n">
@@ -19768,13 +19898,16 @@
       <c r="AO81" s="16"/>
       <c r="AP81" s="16"/>
       <c r="AQ81" s="16"/>
-      <c r="AR81" s="56"/>
-      <c r="AS81" s="56"/>
+      <c r="AR81" s="59"/>
+      <c r="AS81" s="59"/>
       <c r="AT81" s="34"/>
       <c r="AU81" s="34"/>
       <c r="AV81" s="34"/>
       <c r="AW81" s="34"/>
-      <c r="AX81" s="34"/>
+      <c r="AX81" s="62" t="n">
+        <f aca="false">+AX80/Main!F1-1</f>
+        <v>0.37400597834416</v>
+      </c>
       <c r="AY81" s="34"/>
       <c r="AZ81" s="34"/>
       <c r="BA81" s="34"/>
@@ -19989,153 +20122,153 @@
       <c r="DZ82" s="36"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="59" t="s">
-        <v>199</v>
-      </c>
-      <c r="B83" s="59" t="n">
+      <c r="A83" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="63" t="n">
         <f aca="false">+B93+B94+B95-(B106+B107-B109)</f>
         <v>3608</v>
       </c>
-      <c r="C83" s="59" t="n">
+      <c r="C83" s="63" t="n">
         <f aca="false">+C93+C94+C95-(C106+C107-C109)</f>
         <v>3061</v>
       </c>
-      <c r="D83" s="59" t="n">
+      <c r="D83" s="63" t="n">
         <f aca="false">+D93+D94+D95-(D106+D107-D109)</f>
         <v>3174</v>
       </c>
-      <c r="E83" s="59" t="n">
+      <c r="E83" s="63" t="n">
         <f aca="false">+E93+E94+E95-(E106+E107-E109)</f>
         <v>3091</v>
       </c>
-      <c r="F83" s="59" t="n">
+      <c r="F83" s="63" t="n">
         <f aca="false">+F93+F94+F95-(F106+F107-F109)</f>
         <v>2601</v>
       </c>
-      <c r="G83" s="59" t="n">
+      <c r="G83" s="63" t="n">
         <f aca="false">+G93+G94+G95-(G106+G107-G109)</f>
         <v>1686</v>
       </c>
-      <c r="H83" s="59" t="n">
+      <c r="H83" s="63" t="n">
         <f aca="false">+H93+H94+H95-(H106+H107-H109)</f>
         <v>1781</v>
       </c>
-      <c r="I83" s="59" t="n">
+      <c r="I83" s="63" t="n">
         <f aca="false">+I93+I94+I95-(I106+I107-I109)</f>
         <v>1687</v>
       </c>
-      <c r="J83" s="59" t="n">
+      <c r="J83" s="63" t="n">
         <f aca="false">+J93+J94+J95-(J106+J107-J109)</f>
         <v>3382</v>
       </c>
-      <c r="K83" s="59" t="n">
+      <c r="K83" s="63" t="n">
         <f aca="false">+K93+K94+K95-(K106+K107-K109)</f>
         <v>2421</v>
       </c>
-      <c r="L83" s="59" t="n">
+      <c r="L83" s="63" t="n">
         <f aca="false">+L93+L94+L95-(L106+L107-L109)</f>
         <v>2856</v>
       </c>
-      <c r="M83" s="59" t="n">
+      <c r="M83" s="63" t="n">
         <f aca="false">+M93+M94+M95-(M106+M107-M109)</f>
         <v>2421</v>
       </c>
-      <c r="N83" s="59" t="n">
+      <c r="N83" s="63" t="n">
         <f aca="false">+N93+N94+N95-(N106+N107-N109)</f>
         <v>1820</v>
       </c>
-      <c r="O83" s="59" t="n">
+      <c r="O83" s="63" t="n">
         <f aca="false">+O93+O94+O95-(O106+O107-O109)</f>
         <v>1431</v>
       </c>
-      <c r="P83" s="59" t="n">
+      <c r="P83" s="63" t="n">
         <f aca="false">+P93+P94+P95-(P106+P107-P109)</f>
         <v>1804</v>
       </c>
-      <c r="Q83" s="59" t="n">
+      <c r="Q83" s="63" t="n">
         <f aca="false">+Q93+Q94+Q95-(Q106+Q107-Q109)</f>
         <v>1667</v>
       </c>
-      <c r="R83" s="59" t="n">
+      <c r="R83" s="63" t="n">
         <f aca="false">+R93+R94+R95-(R106+R107-R109)</f>
         <v>2227</v>
       </c>
-      <c r="S83" s="59" t="n">
+      <c r="S83" s="63" t="n">
         <f aca="false">+S93+S94+S95-(S106+S107-S109)</f>
         <v>3038</v>
       </c>
-      <c r="T83" s="59"/>
-      <c r="U83" s="59"/>
-      <c r="V83" s="59"/>
-      <c r="W83" s="59"/>
-      <c r="X83" s="59"/>
-      <c r="Y83" s="59"/>
-      <c r="Z83" s="59"/>
-      <c r="AA83" s="59" t="n">
+      <c r="T83" s="63"/>
+      <c r="U83" s="63"/>
+      <c r="V83" s="63"/>
+      <c r="W83" s="63"/>
+      <c r="X83" s="63"/>
+      <c r="Y83" s="63"/>
+      <c r="Z83" s="63"/>
+      <c r="AA83" s="63" t="n">
         <f aca="false">+AA94+AA95-(AA106+AA107+AA112)</f>
         <v>-166</v>
       </c>
-      <c r="AB83" s="59" t="n">
+      <c r="AB83" s="63" t="n">
         <f aca="false">+AB94+AB95-(AB106+AB107+AB112)</f>
         <v>235</v>
       </c>
-      <c r="AC83" s="59" t="n">
+      <c r="AC83" s="63" t="n">
         <f aca="false">+AC94+AC95-(AC106+AC107+AC112)</f>
         <v>126</v>
       </c>
-      <c r="AD83" s="59" t="n">
+      <c r="AD83" s="63" t="n">
         <f aca="false">+AD94+AD95-(AD106+AD107+AD112)</f>
         <v>387</v>
       </c>
-      <c r="AE83" s="59" t="n">
+      <c r="AE83" s="63" t="n">
         <f aca="false">+AE94+AE95-(AE106+AE107+AE112)</f>
         <v>-18</v>
       </c>
-      <c r="AF83" s="59" t="n">
+      <c r="AF83" s="63" t="n">
         <f aca="false">+AF94+AF95-(AF106+AF107+AF112)</f>
         <v>-119</v>
       </c>
-      <c r="AG83" s="59" t="n">
+      <c r="AG83" s="63" t="n">
         <f aca="false">+AG94+AG95-(AG106+AG107)</f>
         <v>631.615960006512</v>
       </c>
-      <c r="AH83" s="59" t="n">
+      <c r="AH83" s="63" t="n">
         <f aca="false">+AH94+AH95-(AH106+AH107)</f>
         <v>703.054331155828</v>
       </c>
-      <c r="AI83" s="59" t="n">
+      <c r="AI83" s="63" t="n">
         <f aca="false">+AI94+AI95-(AI106+AI107)</f>
         <v>696.674321653146</v>
       </c>
-      <c r="AJ83" s="59" t="n">
+      <c r="AJ83" s="63" t="n">
         <f aca="false">+AJ94+AJ95-(AJ106+AJ107)</f>
         <v>1125.87311679661</v>
       </c>
-      <c r="AK83" s="59" t="n">
+      <c r="AK83" s="63" t="n">
         <f aca="false">+AK94+AK95-(AK106+AK107)</f>
         <v>1131.87551247106</v>
       </c>
-      <c r="AL83" s="59" t="n">
+      <c r="AL83" s="63" t="n">
         <f aca="false">+AL94+AL95-(AL106+AL107)</f>
         <v>1232.92448516233</v>
       </c>
-      <c r="AM83" s="59" t="n">
+      <c r="AM83" s="63" t="n">
         <f aca="false">+AM94+AM95-(AM106+AM107)</f>
         <v>1213.89670879521</v>
       </c>
-      <c r="AN83" s="59" t="n">
+      <c r="AN83" s="63" t="n">
         <f aca="false">+AN94+AN95-(AN106+AN107)</f>
         <v>1750.90183165229</v>
       </c>
-      <c r="AO83" s="59" t="n">
+      <c r="AO83" s="63" t="n">
         <f aca="false">+AO94+AO95-(AO106+AO107)</f>
         <v>1721.94025889617</v>
       </c>
-      <c r="AP83" s="59" t="n">
+      <c r="AP83" s="63" t="n">
         <f aca="false">+AP94+AP95-(AP106+AP107)</f>
         <v>1804.88801773369</v>
       </c>
-      <c r="AQ83" s="59" t="n">
+      <c r="AQ83" s="63" t="n">
         <f aca="false">+AQ94+AQ95-(AQ106+AQ107)</f>
         <v>1739.6703812567</v>
       </c>
@@ -20226,158 +20359,158 @@
       <c r="DZ83" s="34"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="59" t="s">
-        <v>200</v>
-      </c>
-      <c r="B84" s="59" t="n">
+      <c r="A84" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="63" t="n">
         <f aca="false">+B45*(1-B68)</f>
         <v>1296.35774465327</v>
       </c>
-      <c r="C84" s="59" t="n">
+      <c r="C84" s="63" t="n">
         <f aca="false">+C45*(1-C68)</f>
         <v>1207.21313672922</v>
       </c>
-      <c r="D84" s="59" t="n">
+      <c r="D84" s="63" t="n">
         <f aca="false">+D45*(1-D68)</f>
         <v>1157.84615384615</v>
       </c>
-      <c r="E84" s="59" t="n">
+      <c r="E84" s="63" t="n">
         <f aca="false">+E45*(1-E68)</f>
         <v>1166.69742913645</v>
       </c>
-      <c r="F84" s="59" t="n">
+      <c r="F84" s="63" t="n">
         <f aca="false">+F45*(1-F68)</f>
         <v>1237.63579474343</v>
       </c>
-      <c r="G84" s="59" t="n">
+      <c r="G84" s="63" t="n">
         <f aca="false">+G45*(1-G68)</f>
         <v>1274.59393939394</v>
       </c>
-      <c r="H84" s="59" t="n">
+      <c r="H84" s="63" t="n">
         <f aca="false">+H45*(1-H68)</f>
         <v>1365.97303499713</v>
       </c>
-      <c r="I84" s="59" t="n">
+      <c r="I84" s="63" t="n">
         <f aca="false">+I45*(1-I68)</f>
         <v>1429.68418141593</v>
       </c>
-      <c r="J84" s="59" t="n">
+      <c r="J84" s="63" t="n">
         <f aca="false">+J45*(1-J68)</f>
         <v>580.929752066116</v>
       </c>
-      <c r="K84" s="59" t="n">
+      <c r="K84" s="63" t="n">
         <f aca="false">+K45*(1-K68)</f>
         <v>1536.32383419689</v>
       </c>
-      <c r="L84" s="59" t="n">
+      <c r="L84" s="63" t="n">
         <f aca="false">+L45*(1-L68)</f>
         <v>1642.76591576885</v>
       </c>
-      <c r="M84" s="59" t="n">
+      <c r="M84" s="63" t="n">
         <f aca="false">+M45*(1-M68)</f>
         <v>1654.25966850829</v>
       </c>
-      <c r="N84" s="59" t="n">
+      <c r="N84" s="63" t="n">
         <f aca="false">+N45*(1-N68)</f>
         <v>1795.23052245646</v>
       </c>
-      <c r="O84" s="59" t="n">
+      <c r="O84" s="63" t="n">
         <f aca="false">+O45*(1-O68)</f>
         <v>1697.43883864826</v>
       </c>
-      <c r="P84" s="59" t="n">
+      <c r="P84" s="63" t="n">
         <f aca="false">+P45*(1-P68)</f>
         <v>1760.65660722451</v>
       </c>
-      <c r="Q84" s="59" t="n">
+      <c r="Q84" s="63" t="n">
         <f aca="false">+Q45*(1-Q68)</f>
         <v>1853.5406360424</v>
       </c>
-      <c r="R84" s="59" t="n">
+      <c r="R84" s="63" t="n">
         <f aca="false">+R45*(1-R68)</f>
         <v>1885.88026424443</v>
       </c>
-      <c r="S84" s="59" t="n">
+      <c r="S84" s="63" t="n">
         <f aca="false">+S45*(1-S68)</f>
         <v>1712</v>
       </c>
-      <c r="T84" s="59"/>
-      <c r="U84" s="59"/>
-      <c r="V84" s="59"/>
-      <c r="W84" s="59"/>
-      <c r="X84" s="59"/>
-      <c r="Y84" s="59"/>
-      <c r="Z84" s="59"/>
-      <c r="AA84" s="59" t="n">
+      <c r="T84" s="63"/>
+      <c r="U84" s="63"/>
+      <c r="V84" s="63"/>
+      <c r="W84" s="63"/>
+      <c r="X84" s="63"/>
+      <c r="Y84" s="63"/>
+      <c r="Z84" s="63"/>
+      <c r="AA84" s="63" t="n">
         <f aca="false">+AA45*(1-AA68)</f>
         <v>5336.31195563116</v>
       </c>
-      <c r="AB84" s="59" t="n">
+      <c r="AB84" s="63" t="n">
         <f aca="false">+AB45*(1-AB68)</f>
         <v>4903.10200560848</v>
       </c>
-      <c r="AC84" s="59" t="n">
+      <c r="AC84" s="63" t="n">
         <f aca="false">+AC45*(1-AC68)</f>
         <v>4826.67052567605</v>
       </c>
-      <c r="AD84" s="59" t="n">
+      <c r="AD84" s="63" t="n">
         <f aca="false">+AD45*(1-AD68)</f>
         <v>5308.58456071057</v>
       </c>
-      <c r="AE84" s="59" t="n">
+      <c r="AE84" s="63" t="n">
         <f aca="false">+AE45*(1-AE68)</f>
         <v>5407.21336333292</v>
       </c>
-      <c r="AF84" s="59" t="n">
+      <c r="AF84" s="63" t="n">
         <f aca="false">+AF45*(1-AF68)</f>
         <v>7106.57600468975</v>
       </c>
-      <c r="AG84" s="59" t="n">
+      <c r="AG84" s="63" t="n">
         <f aca="false">+AG45*(1-AG68)</f>
         <v>8174.76734662479</v>
       </c>
-      <c r="AH84" s="59" t="n">
+      <c r="AH84" s="63" t="n">
         <f aca="false">+AH45*(1-AH68)</f>
         <v>9128.3301213188</v>
       </c>
-      <c r="AI84" s="59" t="n">
+      <c r="AI84" s="63" t="n">
         <f aca="false">+AI45*(1-AI68)</f>
         <v>10686.4105670364</v>
       </c>
-      <c r="AJ84" s="59" t="n">
+      <c r="AJ84" s="63" t="n">
         <f aca="false">+AJ45*(1-AJ68)</f>
         <v>12392.2692735422</v>
       </c>
-      <c r="AK84" s="59" t="n">
+      <c r="AK84" s="63" t="n">
         <f aca="false">+AK45*(1-AK68)</f>
         <v>13574.3970547885</v>
       </c>
-      <c r="AL84" s="59" t="n">
+      <c r="AL84" s="63" t="n">
         <f aca="false">+AL45*(1-AL68)</f>
         <v>14713.016609251</v>
       </c>
-      <c r="AM84" s="59" t="n">
+      <c r="AM84" s="63" t="n">
         <f aca="false">+AM45*(1-AM68)</f>
         <v>17497.4122824425</v>
       </c>
-      <c r="AN84" s="59" t="n">
+      <c r="AN84" s="63" t="n">
         <f aca="false">+AN45*(1-AN68)</f>
         <v>18552.1245981303</v>
       </c>
-      <c r="AO84" s="59" t="n">
+      <c r="AO84" s="63" t="n">
         <f aca="false">+AO45*(1-AO68)</f>
         <v>19461.7640240958</v>
       </c>
-      <c r="AP84" s="59" t="n">
+      <c r="AP84" s="63" t="n">
         <f aca="false">+AP45*(1-AP68)</f>
         <v>20197.3539958282</v>
       </c>
-      <c r="AQ84" s="59" t="n">
+      <c r="AQ84" s="63" t="n">
         <f aca="false">+AQ45*(1-AQ68)</f>
         <v>20733.3689943844</v>
       </c>
-      <c r="AR84" s="40"/>
-      <c r="AS84" s="40"/>
+      <c r="AR84" s="41"/>
+      <c r="AS84" s="41"/>
       <c r="AT84" s="34"/>
       <c r="AU84" s="34"/>
       <c r="AV84" s="34"/>
@@ -20465,210 +20598,210 @@
       <c r="DZ84" s="34"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="59" t="s">
-        <v>201</v>
-      </c>
-      <c r="B85" s="59" t="n">
+      <c r="A85" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="B85" s="63" t="n">
         <f aca="false">+B45+B128+B131+B132</f>
         <v>1963</v>
       </c>
-      <c r="C85" s="59" t="n">
+      <c r="C85" s="63" t="n">
         <f aca="false">+C45+C128+C131+C132</f>
         <v>1839</v>
       </c>
-      <c r="D85" s="59" t="n">
+      <c r="D85" s="63" t="n">
         <f aca="false">+D45+D128+D131+D132</f>
         <v>1818</v>
       </c>
-      <c r="E85" s="59" t="n">
+      <c r="E85" s="63" t="n">
         <f aca="false">+E45+E128+E131+E132</f>
         <v>1784</v>
       </c>
-      <c r="F85" s="59" t="n">
+      <c r="F85" s="63" t="n">
         <f aca="false">+F45+F128+F131+F132</f>
         <v>1768</v>
       </c>
-      <c r="G85" s="59" t="n">
+      <c r="G85" s="63" t="n">
         <f aca="false">+G45+G128+G131+G132</f>
         <v>1737</v>
       </c>
-      <c r="H85" s="59" t="n">
+      <c r="H85" s="63" t="n">
         <f aca="false">+H45+H128+H131+H132</f>
         <v>1823</v>
       </c>
-      <c r="I85" s="59" t="n">
+      <c r="I85" s="63" t="n">
         <f aca="false">+I45+I128+I131+I132</f>
         <v>1833</v>
       </c>
-      <c r="J85" s="59" t="n">
+      <c r="J85" s="63" t="n">
         <f aca="false">+J45+J128+J131+J132</f>
         <v>1009</v>
       </c>
-      <c r="K85" s="59" t="n">
+      <c r="K85" s="63" t="n">
         <f aca="false">+K45+K128+K131+K132</f>
         <v>2000</v>
       </c>
-      <c r="L85" s="59" t="n">
+      <c r="L85" s="63" t="n">
         <f aca="false">+L45+L128+L131+L132</f>
         <v>2114</v>
       </c>
-      <c r="M85" s="59" t="n">
+      <c r="M85" s="63" t="n">
         <f aca="false">+M45+M128+M131+M132</f>
         <v>2137</v>
       </c>
-      <c r="N85" s="59" t="n">
+      <c r="N85" s="63" t="n">
         <f aca="false">+N45+N128+N131+N132</f>
         <v>2228</v>
       </c>
-      <c r="O85" s="59" t="n">
+      <c r="O85" s="63" t="n">
         <f aca="false">+O45+O128+O131+O132</f>
         <v>2217</v>
       </c>
-      <c r="P85" s="59" t="n">
+      <c r="P85" s="63" t="n">
         <f aca="false">+P45+P128+P131+P132</f>
         <v>2280</v>
       </c>
-      <c r="Q85" s="59" t="n">
+      <c r="Q85" s="63" t="n">
         <f aca="false">+Q45+Q128+Q131+Q132</f>
         <v>2336</v>
       </c>
-      <c r="R85" s="59" t="n">
+      <c r="R85" s="63" t="n">
         <f aca="false">+R45+R128+R131+R132</f>
         <v>2702</v>
       </c>
-      <c r="S85" s="59" t="n">
+      <c r="S85" s="63" t="n">
         <f aca="false">+S45+S128+S131+S132</f>
         <v>2578</v>
       </c>
-      <c r="T85" s="59"/>
-      <c r="U85" s="59"/>
-      <c r="V85" s="59"/>
-      <c r="W85" s="59"/>
-      <c r="X85" s="59"/>
-      <c r="Y85" s="59"/>
-      <c r="Z85" s="59"/>
-      <c r="AA85" s="59" t="n">
+      <c r="T85" s="63"/>
+      <c r="U85" s="63"/>
+      <c r="V85" s="63"/>
+      <c r="W85" s="63"/>
+      <c r="X85" s="63"/>
+      <c r="Y85" s="63"/>
+      <c r="Z85" s="63"/>
+      <c r="AA85" s="63" t="n">
         <f aca="false">+AA45+AA128+AA131+AA132</f>
         <v>3608.47567609574</v>
       </c>
-      <c r="AB85" s="59" t="n">
+      <c r="AB85" s="63" t="n">
         <f aca="false">+AB45+AB128+AB131+AB132</f>
         <v>6848.11764961537</v>
       </c>
-      <c r="AC85" s="59" t="n">
+      <c r="AC85" s="63" t="n">
         <f aca="false">+AC45+AC128+AC131+AC132</f>
         <v>7403.42730694741</v>
       </c>
-      <c r="AD85" s="59" t="n">
+      <c r="AD85" s="63" t="n">
         <f aca="false">+AD45+AD128+AD131+AD132</f>
         <v>7160.53706696481</v>
       </c>
-      <c r="AE85" s="59" t="n">
+      <c r="AE85" s="63" t="n">
         <f aca="false">+AE45+AE128+AE131+AE132</f>
         <v>7259.62802488093</v>
       </c>
-      <c r="AF85" s="59" t="n">
+      <c r="AF85" s="63" t="n">
         <f aca="false">+AF45+AF128+AF131+AF132</f>
         <v>9060.43346823334</v>
       </c>
-      <c r="AG85" s="59"/>
-      <c r="AH85" s="59"/>
-      <c r="AI85" s="59"/>
-      <c r="AJ85" s="59"/>
-      <c r="AK85" s="59"/>
-      <c r="AL85" s="59"/>
-      <c r="AM85" s="59"/>
-      <c r="AN85" s="59"/>
-      <c r="AO85" s="59"/>
-      <c r="AP85" s="59"/>
-      <c r="AQ85" s="59"/>
-      <c r="AR85" s="40"/>
-      <c r="AS85" s="40"/>
-      <c r="AT85" s="40"/>
-      <c r="AU85" s="40"/>
-      <c r="AV85" s="40"/>
-      <c r="AW85" s="40"/>
-      <c r="AX85" s="40"/>
-      <c r="AY85" s="40"/>
-      <c r="AZ85" s="40"/>
-      <c r="BA85" s="40"/>
-      <c r="BB85" s="40"/>
-      <c r="BC85" s="40"/>
-      <c r="BD85" s="40"/>
-      <c r="BE85" s="40"/>
-      <c r="BF85" s="40"/>
-      <c r="BG85" s="40"/>
-      <c r="BH85" s="40"/>
-      <c r="BI85" s="40"/>
-      <c r="BJ85" s="40"/>
-      <c r="BK85" s="40"/>
-      <c r="BL85" s="40"/>
-      <c r="BM85" s="40"/>
-      <c r="BN85" s="40"/>
-      <c r="BO85" s="40"/>
-      <c r="BP85" s="40"/>
-      <c r="BQ85" s="40"/>
-      <c r="BR85" s="40"/>
-      <c r="BS85" s="40"/>
-      <c r="BT85" s="40"/>
-      <c r="BU85" s="40"/>
-      <c r="BV85" s="40"/>
-      <c r="BW85" s="40"/>
-      <c r="BX85" s="40"/>
-      <c r="BY85" s="40"/>
-      <c r="BZ85" s="40"/>
-      <c r="CA85" s="40"/>
-      <c r="CB85" s="40"/>
-      <c r="CC85" s="40"/>
-      <c r="CD85" s="40"/>
-      <c r="CE85" s="40"/>
-      <c r="CF85" s="40"/>
-      <c r="CG85" s="40"/>
-      <c r="CH85" s="40"/>
-      <c r="CI85" s="40"/>
-      <c r="CJ85" s="40"/>
-      <c r="CK85" s="40"/>
-      <c r="CL85" s="40"/>
-      <c r="CM85" s="40"/>
-      <c r="CN85" s="40"/>
-      <c r="CO85" s="40"/>
-      <c r="CP85" s="40"/>
-      <c r="CQ85" s="40"/>
-      <c r="CR85" s="40"/>
-      <c r="CS85" s="40"/>
-      <c r="CT85" s="40"/>
-      <c r="CU85" s="40"/>
-      <c r="CV85" s="40"/>
-      <c r="CW85" s="40"/>
-      <c r="CX85" s="40"/>
-      <c r="CY85" s="40"/>
-      <c r="CZ85" s="40"/>
-      <c r="DA85" s="40"/>
-      <c r="DB85" s="40"/>
-      <c r="DC85" s="40"/>
-      <c r="DD85" s="40"/>
-      <c r="DE85" s="40"/>
-      <c r="DF85" s="40"/>
-      <c r="DG85" s="40"/>
-      <c r="DH85" s="40"/>
-      <c r="DI85" s="40"/>
-      <c r="DJ85" s="40"/>
-      <c r="DK85" s="40"/>
-      <c r="DL85" s="40"/>
-      <c r="DM85" s="40"/>
-      <c r="DN85" s="40"/>
-      <c r="DO85" s="40"/>
-      <c r="DP85" s="40"/>
-      <c r="DQ85" s="40"/>
-      <c r="DR85" s="40"/>
-      <c r="DS85" s="40"/>
-      <c r="DT85" s="40"/>
-      <c r="DU85" s="40"/>
-      <c r="DV85" s="40"/>
-      <c r="DW85" s="40"/>
-      <c r="DX85" s="40"/>
-      <c r="DY85" s="40"/>
-      <c r="DZ85" s="40"/>
+      <c r="AG85" s="63"/>
+      <c r="AH85" s="63"/>
+      <c r="AI85" s="63"/>
+      <c r="AJ85" s="63"/>
+      <c r="AK85" s="63"/>
+      <c r="AL85" s="63"/>
+      <c r="AM85" s="63"/>
+      <c r="AN85" s="63"/>
+      <c r="AO85" s="63"/>
+      <c r="AP85" s="63"/>
+      <c r="AQ85" s="63"/>
+      <c r="AR85" s="41"/>
+      <c r="AS85" s="41"/>
+      <c r="AT85" s="41"/>
+      <c r="AU85" s="41"/>
+      <c r="AV85" s="41"/>
+      <c r="AW85" s="41"/>
+      <c r="AX85" s="41"/>
+      <c r="AY85" s="41"/>
+      <c r="AZ85" s="41"/>
+      <c r="BA85" s="41"/>
+      <c r="BB85" s="41"/>
+      <c r="BC85" s="41"/>
+      <c r="BD85" s="41"/>
+      <c r="BE85" s="41"/>
+      <c r="BF85" s="41"/>
+      <c r="BG85" s="41"/>
+      <c r="BH85" s="41"/>
+      <c r="BI85" s="41"/>
+      <c r="BJ85" s="41"/>
+      <c r="BK85" s="41"/>
+      <c r="BL85" s="41"/>
+      <c r="BM85" s="41"/>
+      <c r="BN85" s="41"/>
+      <c r="BO85" s="41"/>
+      <c r="BP85" s="41"/>
+      <c r="BQ85" s="41"/>
+      <c r="BR85" s="41"/>
+      <c r="BS85" s="41"/>
+      <c r="BT85" s="41"/>
+      <c r="BU85" s="41"/>
+      <c r="BV85" s="41"/>
+      <c r="BW85" s="41"/>
+      <c r="BX85" s="41"/>
+      <c r="BY85" s="41"/>
+      <c r="BZ85" s="41"/>
+      <c r="CA85" s="41"/>
+      <c r="CB85" s="41"/>
+      <c r="CC85" s="41"/>
+      <c r="CD85" s="41"/>
+      <c r="CE85" s="41"/>
+      <c r="CF85" s="41"/>
+      <c r="CG85" s="41"/>
+      <c r="CH85" s="41"/>
+      <c r="CI85" s="41"/>
+      <c r="CJ85" s="41"/>
+      <c r="CK85" s="41"/>
+      <c r="CL85" s="41"/>
+      <c r="CM85" s="41"/>
+      <c r="CN85" s="41"/>
+      <c r="CO85" s="41"/>
+      <c r="CP85" s="41"/>
+      <c r="CQ85" s="41"/>
+      <c r="CR85" s="41"/>
+      <c r="CS85" s="41"/>
+      <c r="CT85" s="41"/>
+      <c r="CU85" s="41"/>
+      <c r="CV85" s="41"/>
+      <c r="CW85" s="41"/>
+      <c r="CX85" s="41"/>
+      <c r="CY85" s="41"/>
+      <c r="CZ85" s="41"/>
+      <c r="DA85" s="41"/>
+      <c r="DB85" s="41"/>
+      <c r="DC85" s="41"/>
+      <c r="DD85" s="41"/>
+      <c r="DE85" s="41"/>
+      <c r="DF85" s="41"/>
+      <c r="DG85" s="41"/>
+      <c r="DH85" s="41"/>
+      <c r="DI85" s="41"/>
+      <c r="DJ85" s="41"/>
+      <c r="DK85" s="41"/>
+      <c r="DL85" s="41"/>
+      <c r="DM85" s="41"/>
+      <c r="DN85" s="41"/>
+      <c r="DO85" s="41"/>
+      <c r="DP85" s="41"/>
+      <c r="DQ85" s="41"/>
+      <c r="DR85" s="41"/>
+      <c r="DS85" s="41"/>
+      <c r="DT85" s="41"/>
+      <c r="DU85" s="41"/>
+      <c r="DV85" s="41"/>
+      <c r="DW85" s="41"/>
+      <c r="DX85" s="41"/>
+      <c r="DY85" s="41"/>
+      <c r="DZ85" s="41"/>
     </row>
     <row r="86" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="27" t="s">
@@ -20862,186 +20995,186 @@
       <c r="DZ86" s="25"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="59" t="s">
-        <v>202</v>
-      </c>
-      <c r="B87" s="59"/>
-      <c r="C87" s="59"/>
-      <c r="D87" s="59"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59"/>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
-      <c r="M87" s="59"/>
-      <c r="N87" s="59"/>
-      <c r="O87" s="59"/>
-      <c r="P87" s="59"/>
-      <c r="Q87" s="59"/>
-      <c r="R87" s="59"/>
-      <c r="S87" s="59"/>
-      <c r="T87" s="59"/>
-      <c r="U87" s="59"/>
-      <c r="V87" s="59"/>
-      <c r="W87" s="59"/>
-      <c r="X87" s="59"/>
-      <c r="Y87" s="59"/>
-      <c r="Z87" s="59"/>
-      <c r="AA87" s="59"/>
-      <c r="AB87" s="59" t="n">
+      <c r="A87" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" s="63"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="63"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="63"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="63"/>
+      <c r="N87" s="63"/>
+      <c r="O87" s="63"/>
+      <c r="P87" s="63"/>
+      <c r="Q87" s="63"/>
+      <c r="R87" s="63"/>
+      <c r="S87" s="63"/>
+      <c r="T87" s="63"/>
+      <c r="U87" s="63"/>
+      <c r="V87" s="63"/>
+      <c r="W87" s="63"/>
+      <c r="X87" s="63"/>
+      <c r="Y87" s="63"/>
+      <c r="Z87" s="63"/>
+      <c r="AA87" s="63"/>
+      <c r="AB87" s="63" t="n">
         <f aca="false">+AB84+AB128-AB137-(AB83-AA83)</f>
         <v>4942.10200560848</v>
       </c>
-      <c r="AC87" s="59" t="n">
+      <c r="AC87" s="63" t="n">
         <f aca="false">+AC84+AC128-AC137-(AC83-AB83)</f>
         <v>5349.67052567605</v>
       </c>
-      <c r="AD87" s="59" t="n">
+      <c r="AD87" s="63" t="n">
         <f aca="false">+AD84+AD128-AD137-(AD83-AC83)</f>
         <v>5559.58456071057</v>
       </c>
-      <c r="AE87" s="59" t="n">
+      <c r="AE87" s="63" t="n">
         <f aca="false">+AE84+AE128-AE137-(AE83-AD83)</f>
         <v>6486.21336333292</v>
       </c>
-      <c r="AF87" s="59" t="n">
+      <c r="AF87" s="63" t="n">
         <f aca="false">+AF84+AF128-AF137-(AF83-AE83)</f>
         <v>7846.57600468975</v>
       </c>
-      <c r="AG87" s="59" t="n">
+      <c r="AG87" s="63" t="n">
         <f aca="false">+AG84+AG128-AG137-(AG83-AF83)</f>
         <v>8166.21956661828</v>
       </c>
-      <c r="AH87" s="59" t="n">
+      <c r="AH87" s="63" t="n">
         <f aca="false">+AH84+AH128-AH137-(AH83-AG83)</f>
         <v>9876.87708906948</v>
       </c>
-      <c r="AI87" s="59" t="n">
+      <c r="AI87" s="63" t="n">
         <f aca="false">+AI84+AI128-AI137-(AI83-AH83)</f>
         <v>11590.6745226346</v>
       </c>
-      <c r="AJ87" s="59" t="n">
+      <c r="AJ87" s="63" t="n">
         <f aca="false">+AJ84+AJ128-AJ137-(AJ83-AI83)</f>
         <v>12941.7639796428</v>
       </c>
-      <c r="AK87" s="59" t="n">
+      <c r="AK87" s="63" t="n">
         <f aca="false">+AK84+AK128-AK137-(AK83-AJ83)</f>
         <v>14625.3836404577</v>
       </c>
-      <c r="AL87" s="59" t="n">
+      <c r="AL87" s="63" t="n">
         <f aca="false">+AL84+AL128-AL137-(AL83-AK83)</f>
         <v>15742.9458465974</v>
       </c>
-      <c r="AM87" s="59" t="n">
+      <c r="AM87" s="63" t="n">
         <f aca="false">+AM84+AM128-AM137-(AM83-AL83)</f>
         <v>18715.2769614496</v>
       </c>
-      <c r="AN87" s="59" t="n">
+      <c r="AN87" s="63" t="n">
         <f aca="false">+AN84+AN128-AN137-(AN83-AM83)</f>
         <v>19273.8982230452</v>
       </c>
-      <c r="AO87" s="59" t="n">
+      <c r="AO87" s="63" t="n">
         <f aca="false">+AO84+AO128-AO137-(AO83-AN83)</f>
         <v>20799.8554945348</v>
       </c>
-      <c r="AP87" s="59" t="n">
+      <c r="AP87" s="63" t="n">
         <f aca="false">+AP84+AP128-AP137-(AP83-AO83)</f>
         <v>21462.8100316039</v>
       </c>
-      <c r="AQ87" s="59" t="n">
+      <c r="AQ87" s="63" t="n">
         <f aca="false">+AQ84+AQ128-AQ137-(AQ83-AP83)</f>
         <v>22173.958501367</v>
       </c>
-      <c r="AR87" s="40"/>
-      <c r="AS87" s="40"/>
-      <c r="AT87" s="40"/>
-      <c r="AU87" s="40"/>
-      <c r="AV87" s="40"/>
-      <c r="AW87" s="40"/>
-      <c r="AX87" s="40"/>
-      <c r="AY87" s="40"/>
-      <c r="AZ87" s="40"/>
-      <c r="BA87" s="40"/>
-      <c r="BB87" s="40"/>
-      <c r="BC87" s="40"/>
-      <c r="BD87" s="40"/>
-      <c r="BE87" s="40"/>
-      <c r="BF87" s="40"/>
-      <c r="BG87" s="40"/>
-      <c r="BH87" s="40"/>
-      <c r="BI87" s="40"/>
-      <c r="BJ87" s="40"/>
-      <c r="BK87" s="40"/>
-      <c r="BL87" s="40"/>
-      <c r="BM87" s="40"/>
-      <c r="BN87" s="40"/>
-      <c r="BO87" s="40"/>
-      <c r="BP87" s="40"/>
-      <c r="BQ87" s="40"/>
-      <c r="BR87" s="40"/>
-      <c r="BS87" s="40"/>
-      <c r="BT87" s="40"/>
-      <c r="BU87" s="40"/>
-      <c r="BV87" s="40"/>
-      <c r="BW87" s="40"/>
-      <c r="BX87" s="40"/>
-      <c r="BY87" s="40"/>
-      <c r="BZ87" s="40"/>
-      <c r="CA87" s="40"/>
-      <c r="CB87" s="40"/>
-      <c r="CC87" s="40"/>
-      <c r="CD87" s="40"/>
-      <c r="CE87" s="40"/>
-      <c r="CF87" s="40"/>
-      <c r="CG87" s="40"/>
-      <c r="CH87" s="40"/>
-      <c r="CI87" s="40"/>
-      <c r="CJ87" s="40"/>
-      <c r="CK87" s="40"/>
-      <c r="CL87" s="40"/>
-      <c r="CM87" s="40"/>
-      <c r="CN87" s="40"/>
-      <c r="CO87" s="40"/>
-      <c r="CP87" s="40"/>
-      <c r="CQ87" s="40"/>
-      <c r="CR87" s="40"/>
-      <c r="CS87" s="40"/>
-      <c r="CT87" s="40"/>
-      <c r="CU87" s="40"/>
-      <c r="CV87" s="40"/>
-      <c r="CW87" s="40"/>
-      <c r="CX87" s="40"/>
-      <c r="CY87" s="40"/>
-      <c r="CZ87" s="40"/>
-      <c r="DA87" s="40"/>
-      <c r="DB87" s="40"/>
-      <c r="DC87" s="40"/>
-      <c r="DD87" s="40"/>
-      <c r="DE87" s="40"/>
-      <c r="DF87" s="40"/>
-      <c r="DG87" s="40"/>
-      <c r="DH87" s="40"/>
-      <c r="DI87" s="40"/>
-      <c r="DJ87" s="40"/>
-      <c r="DK87" s="40"/>
-      <c r="DL87" s="40"/>
-      <c r="DM87" s="40"/>
-      <c r="DN87" s="40"/>
-      <c r="DO87" s="40"/>
-      <c r="DP87" s="40"/>
-      <c r="DQ87" s="40"/>
-      <c r="DR87" s="40"/>
-      <c r="DS87" s="40"/>
-      <c r="DT87" s="40"/>
-      <c r="DU87" s="40"/>
-      <c r="DV87" s="40"/>
-      <c r="DW87" s="40"/>
-      <c r="DX87" s="40"/>
-      <c r="DY87" s="40"/>
-      <c r="DZ87" s="40"/>
+      <c r="AR87" s="41"/>
+      <c r="AS87" s="41"/>
+      <c r="AT87" s="41"/>
+      <c r="AU87" s="41"/>
+      <c r="AV87" s="41"/>
+      <c r="AW87" s="41"/>
+      <c r="AX87" s="41"/>
+      <c r="AY87" s="41"/>
+      <c r="AZ87" s="41"/>
+      <c r="BA87" s="41"/>
+      <c r="BB87" s="41"/>
+      <c r="BC87" s="41"/>
+      <c r="BD87" s="41"/>
+      <c r="BE87" s="41"/>
+      <c r="BF87" s="41"/>
+      <c r="BG87" s="41"/>
+      <c r="BH87" s="41"/>
+      <c r="BI87" s="41"/>
+      <c r="BJ87" s="41"/>
+      <c r="BK87" s="41"/>
+      <c r="BL87" s="41"/>
+      <c r="BM87" s="41"/>
+      <c r="BN87" s="41"/>
+      <c r="BO87" s="41"/>
+      <c r="BP87" s="41"/>
+      <c r="BQ87" s="41"/>
+      <c r="BR87" s="41"/>
+      <c r="BS87" s="41"/>
+      <c r="BT87" s="41"/>
+      <c r="BU87" s="41"/>
+      <c r="BV87" s="41"/>
+      <c r="BW87" s="41"/>
+      <c r="BX87" s="41"/>
+      <c r="BY87" s="41"/>
+      <c r="BZ87" s="41"/>
+      <c r="CA87" s="41"/>
+      <c r="CB87" s="41"/>
+      <c r="CC87" s="41"/>
+      <c r="CD87" s="41"/>
+      <c r="CE87" s="41"/>
+      <c r="CF87" s="41"/>
+      <c r="CG87" s="41"/>
+      <c r="CH87" s="41"/>
+      <c r="CI87" s="41"/>
+      <c r="CJ87" s="41"/>
+      <c r="CK87" s="41"/>
+      <c r="CL87" s="41"/>
+      <c r="CM87" s="41"/>
+      <c r="CN87" s="41"/>
+      <c r="CO87" s="41"/>
+      <c r="CP87" s="41"/>
+      <c r="CQ87" s="41"/>
+      <c r="CR87" s="41"/>
+      <c r="CS87" s="41"/>
+      <c r="CT87" s="41"/>
+      <c r="CU87" s="41"/>
+      <c r="CV87" s="41"/>
+      <c r="CW87" s="41"/>
+      <c r="CX87" s="41"/>
+      <c r="CY87" s="41"/>
+      <c r="CZ87" s="41"/>
+      <c r="DA87" s="41"/>
+      <c r="DB87" s="41"/>
+      <c r="DC87" s="41"/>
+      <c r="DD87" s="41"/>
+      <c r="DE87" s="41"/>
+      <c r="DF87" s="41"/>
+      <c r="DG87" s="41"/>
+      <c r="DH87" s="41"/>
+      <c r="DI87" s="41"/>
+      <c r="DJ87" s="41"/>
+      <c r="DK87" s="41"/>
+      <c r="DL87" s="41"/>
+      <c r="DM87" s="41"/>
+      <c r="DN87" s="41"/>
+      <c r="DO87" s="41"/>
+      <c r="DP87" s="41"/>
+      <c r="DQ87" s="41"/>
+      <c r="DR87" s="41"/>
+      <c r="DS87" s="41"/>
+      <c r="DT87" s="41"/>
+      <c r="DU87" s="41"/>
+      <c r="DV87" s="41"/>
+      <c r="DW87" s="41"/>
+      <c r="DX87" s="41"/>
+      <c r="DY87" s="41"/>
+      <c r="DZ87" s="41"/>
     </row>
     <row r="88" s="17" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="35"/>
@@ -21087,93 +21220,93 @@
       <c r="AO88" s="35"/>
       <c r="AP88" s="35"/>
       <c r="AQ88" s="35"/>
-      <c r="AR88" s="40"/>
-      <c r="AS88" s="40"/>
-      <c r="AT88" s="40"/>
-      <c r="AU88" s="40"/>
-      <c r="AV88" s="40"/>
-      <c r="AW88" s="40"/>
-      <c r="AX88" s="40"/>
-      <c r="AY88" s="40"/>
-      <c r="AZ88" s="40"/>
-      <c r="BA88" s="40"/>
-      <c r="BB88" s="40"/>
-      <c r="BC88" s="40"/>
-      <c r="BD88" s="40"/>
-      <c r="BE88" s="40"/>
-      <c r="BF88" s="40"/>
-      <c r="BG88" s="40"/>
-      <c r="BH88" s="40"/>
-      <c r="BI88" s="40"/>
-      <c r="BJ88" s="40"/>
-      <c r="BK88" s="40"/>
-      <c r="BL88" s="40"/>
-      <c r="BM88" s="40"/>
-      <c r="BN88" s="40"/>
-      <c r="BO88" s="40"/>
-      <c r="BP88" s="40"/>
-      <c r="BQ88" s="40"/>
-      <c r="BR88" s="40"/>
-      <c r="BS88" s="40"/>
-      <c r="BT88" s="40"/>
-      <c r="BU88" s="40"/>
-      <c r="BV88" s="40"/>
-      <c r="BW88" s="40"/>
-      <c r="BX88" s="40"/>
-      <c r="BY88" s="40"/>
-      <c r="BZ88" s="40"/>
-      <c r="CA88" s="40"/>
-      <c r="CB88" s="40"/>
-      <c r="CC88" s="40"/>
-      <c r="CD88" s="40"/>
-      <c r="CE88" s="40"/>
-      <c r="CF88" s="40"/>
-      <c r="CG88" s="40"/>
-      <c r="CH88" s="40"/>
-      <c r="CI88" s="40"/>
-      <c r="CJ88" s="40"/>
-      <c r="CK88" s="40"/>
-      <c r="CL88" s="40"/>
-      <c r="CM88" s="40"/>
-      <c r="CN88" s="40"/>
-      <c r="CO88" s="40"/>
-      <c r="CP88" s="40"/>
-      <c r="CQ88" s="40"/>
-      <c r="CR88" s="40"/>
-      <c r="CS88" s="40"/>
-      <c r="CT88" s="40"/>
-      <c r="CU88" s="40"/>
-      <c r="CV88" s="40"/>
-      <c r="CW88" s="40"/>
-      <c r="CX88" s="40"/>
-      <c r="CY88" s="40"/>
-      <c r="CZ88" s="40"/>
-      <c r="DA88" s="40"/>
-      <c r="DB88" s="40"/>
-      <c r="DC88" s="40"/>
-      <c r="DD88" s="40"/>
-      <c r="DE88" s="40"/>
-      <c r="DF88" s="40"/>
-      <c r="DG88" s="40"/>
-      <c r="DH88" s="40"/>
-      <c r="DI88" s="40"/>
-      <c r="DJ88" s="40"/>
-      <c r="DK88" s="40"/>
-      <c r="DL88" s="40"/>
-      <c r="DM88" s="40"/>
-      <c r="DN88" s="40"/>
-      <c r="DO88" s="40"/>
-      <c r="DP88" s="40"/>
-      <c r="DQ88" s="40"/>
-      <c r="DR88" s="40"/>
-      <c r="DS88" s="40"/>
-      <c r="DT88" s="40"/>
-      <c r="DU88" s="40"/>
-      <c r="DV88" s="40"/>
-      <c r="DW88" s="40"/>
-      <c r="DX88" s="40"/>
-      <c r="DY88" s="40"/>
-      <c r="DZ88" s="40"/>
+      <c r="AR88" s="41"/>
+      <c r="AS88" s="41"/>
+      <c r="AT88" s="41"/>
+      <c r="AU88" s="41"/>
+      <c r="AV88" s="41"/>
+      <c r="AW88" s="41"/>
+      <c r="AX88" s="41"/>
+      <c r="AY88" s="41"/>
+      <c r="AZ88" s="41"/>
+      <c r="BA88" s="41"/>
+      <c r="BB88" s="41"/>
+      <c r="BC88" s="41"/>
+      <c r="BD88" s="41"/>
+      <c r="BE88" s="41"/>
+      <c r="BF88" s="41"/>
+      <c r="BG88" s="41"/>
+      <c r="BH88" s="41"/>
+      <c r="BI88" s="41"/>
+      <c r="BJ88" s="41"/>
+      <c r="BK88" s="41"/>
+      <c r="BL88" s="41"/>
+      <c r="BM88" s="41"/>
+      <c r="BN88" s="41"/>
+      <c r="BO88" s="41"/>
+      <c r="BP88" s="41"/>
+      <c r="BQ88" s="41"/>
+      <c r="BR88" s="41"/>
+      <c r="BS88" s="41"/>
+      <c r="BT88" s="41"/>
+      <c r="BU88" s="41"/>
+      <c r="BV88" s="41"/>
+      <c r="BW88" s="41"/>
+      <c r="BX88" s="41"/>
+      <c r="BY88" s="41"/>
+      <c r="BZ88" s="41"/>
+      <c r="CA88" s="41"/>
+      <c r="CB88" s="41"/>
+      <c r="CC88" s="41"/>
+      <c r="CD88" s="41"/>
+      <c r="CE88" s="41"/>
+      <c r="CF88" s="41"/>
+      <c r="CG88" s="41"/>
+      <c r="CH88" s="41"/>
+      <c r="CI88" s="41"/>
+      <c r="CJ88" s="41"/>
+      <c r="CK88" s="41"/>
+      <c r="CL88" s="41"/>
+      <c r="CM88" s="41"/>
+      <c r="CN88" s="41"/>
+      <c r="CO88" s="41"/>
+      <c r="CP88" s="41"/>
+      <c r="CQ88" s="41"/>
+      <c r="CR88" s="41"/>
+      <c r="CS88" s="41"/>
+      <c r="CT88" s="41"/>
+      <c r="CU88" s="41"/>
+      <c r="CV88" s="41"/>
+      <c r="CW88" s="41"/>
+      <c r="CX88" s="41"/>
+      <c r="CY88" s="41"/>
+      <c r="CZ88" s="41"/>
+      <c r="DA88" s="41"/>
+      <c r="DB88" s="41"/>
+      <c r="DC88" s="41"/>
+      <c r="DD88" s="41"/>
+      <c r="DE88" s="41"/>
+      <c r="DF88" s="41"/>
+      <c r="DG88" s="41"/>
+      <c r="DH88" s="41"/>
+      <c r="DI88" s="41"/>
+      <c r="DJ88" s="41"/>
+      <c r="DK88" s="41"/>
+      <c r="DL88" s="41"/>
+      <c r="DM88" s="41"/>
+      <c r="DN88" s="41"/>
+      <c r="DO88" s="41"/>
+      <c r="DP88" s="41"/>
+      <c r="DQ88" s="41"/>
+      <c r="DR88" s="41"/>
+      <c r="DS88" s="41"/>
+      <c r="DT88" s="41"/>
+      <c r="DU88" s="41"/>
+      <c r="DV88" s="41"/>
+      <c r="DW88" s="41"/>
+      <c r="DX88" s="41"/>
+      <c r="DY88" s="41"/>
+      <c r="DZ88" s="41"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="35"/>
@@ -21219,95 +21352,95 @@
       <c r="AO89" s="35"/>
       <c r="AP89" s="35"/>
       <c r="AQ89" s="35"/>
-      <c r="AT89" s="40"/>
-      <c r="AU89" s="40"/>
-      <c r="AV89" s="40"/>
-      <c r="AW89" s="40"/>
-      <c r="AX89" s="40"/>
-      <c r="AY89" s="40"/>
-      <c r="AZ89" s="40"/>
-      <c r="BA89" s="40"/>
-      <c r="BB89" s="40"/>
-      <c r="BC89" s="40"/>
-      <c r="BD89" s="40"/>
-      <c r="BE89" s="40"/>
-      <c r="BF89" s="40"/>
-      <c r="BG89" s="40"/>
-      <c r="BH89" s="40"/>
-      <c r="BI89" s="40"/>
-      <c r="BJ89" s="40"/>
-      <c r="BK89" s="40"/>
-      <c r="BL89" s="40"/>
-      <c r="BM89" s="40"/>
-      <c r="BN89" s="40"/>
-      <c r="BO89" s="40"/>
-      <c r="BP89" s="40"/>
-      <c r="BQ89" s="40"/>
-      <c r="BR89" s="40"/>
-      <c r="BS89" s="40"/>
-      <c r="BT89" s="40"/>
-      <c r="BU89" s="40"/>
-      <c r="BV89" s="40"/>
-      <c r="BW89" s="40"/>
-      <c r="BX89" s="40"/>
-      <c r="BY89" s="40"/>
-      <c r="BZ89" s="40"/>
-      <c r="CA89" s="40"/>
-      <c r="CB89" s="40"/>
-      <c r="CC89" s="40"/>
-      <c r="CD89" s="40"/>
-      <c r="CE89" s="40"/>
-      <c r="CF89" s="40"/>
-      <c r="CG89" s="40"/>
-      <c r="CH89" s="40"/>
-      <c r="CI89" s="40"/>
-      <c r="CJ89" s="40"/>
-      <c r="CK89" s="40"/>
-      <c r="CL89" s="40"/>
-      <c r="CM89" s="40"/>
-      <c r="CN89" s="40"/>
-      <c r="CO89" s="40"/>
-      <c r="CP89" s="40"/>
-      <c r="CQ89" s="40"/>
-      <c r="CR89" s="40"/>
-      <c r="CS89" s="40"/>
-      <c r="CT89" s="40"/>
-      <c r="CU89" s="40"/>
-      <c r="CV89" s="40"/>
-      <c r="CW89" s="40"/>
-      <c r="CX89" s="40"/>
-      <c r="CY89" s="40"/>
-      <c r="CZ89" s="40"/>
-      <c r="DA89" s="40"/>
-      <c r="DB89" s="40"/>
-      <c r="DC89" s="40"/>
-      <c r="DD89" s="40"/>
-      <c r="DE89" s="40"/>
-      <c r="DF89" s="40"/>
-      <c r="DG89" s="40"/>
-      <c r="DH89" s="40"/>
-      <c r="DI89" s="40"/>
-      <c r="DJ89" s="40"/>
-      <c r="DK89" s="40"/>
-      <c r="DL89" s="40"/>
-      <c r="DM89" s="40"/>
-      <c r="DN89" s="40"/>
-      <c r="DO89" s="40"/>
-      <c r="DP89" s="40"/>
-      <c r="DQ89" s="40"/>
-      <c r="DR89" s="40"/>
-      <c r="DS89" s="40"/>
-      <c r="DT89" s="40"/>
-      <c r="DU89" s="40"/>
-      <c r="DV89" s="40"/>
-      <c r="DW89" s="40"/>
-      <c r="DX89" s="40"/>
-      <c r="DY89" s="40"/>
-      <c r="DZ89" s="40"/>
+      <c r="AT89" s="41"/>
+      <c r="AU89" s="41"/>
+      <c r="AV89" s="41"/>
+      <c r="AW89" s="41"/>
+      <c r="AX89" s="41"/>
+      <c r="AY89" s="41"/>
+      <c r="AZ89" s="41"/>
+      <c r="BA89" s="41"/>
+      <c r="BB89" s="41"/>
+      <c r="BC89" s="41"/>
+      <c r="BD89" s="41"/>
+      <c r="BE89" s="41"/>
+      <c r="BF89" s="41"/>
+      <c r="BG89" s="41"/>
+      <c r="BH89" s="41"/>
+      <c r="BI89" s="41"/>
+      <c r="BJ89" s="41"/>
+      <c r="BK89" s="41"/>
+      <c r="BL89" s="41"/>
+      <c r="BM89" s="41"/>
+      <c r="BN89" s="41"/>
+      <c r="BO89" s="41"/>
+      <c r="BP89" s="41"/>
+      <c r="BQ89" s="41"/>
+      <c r="BR89" s="41"/>
+      <c r="BS89" s="41"/>
+      <c r="BT89" s="41"/>
+      <c r="BU89" s="41"/>
+      <c r="BV89" s="41"/>
+      <c r="BW89" s="41"/>
+      <c r="BX89" s="41"/>
+      <c r="BY89" s="41"/>
+      <c r="BZ89" s="41"/>
+      <c r="CA89" s="41"/>
+      <c r="CB89" s="41"/>
+      <c r="CC89" s="41"/>
+      <c r="CD89" s="41"/>
+      <c r="CE89" s="41"/>
+      <c r="CF89" s="41"/>
+      <c r="CG89" s="41"/>
+      <c r="CH89" s="41"/>
+      <c r="CI89" s="41"/>
+      <c r="CJ89" s="41"/>
+      <c r="CK89" s="41"/>
+      <c r="CL89" s="41"/>
+      <c r="CM89" s="41"/>
+      <c r="CN89" s="41"/>
+      <c r="CO89" s="41"/>
+      <c r="CP89" s="41"/>
+      <c r="CQ89" s="41"/>
+      <c r="CR89" s="41"/>
+      <c r="CS89" s="41"/>
+      <c r="CT89" s="41"/>
+      <c r="CU89" s="41"/>
+      <c r="CV89" s="41"/>
+      <c r="CW89" s="41"/>
+      <c r="CX89" s="41"/>
+      <c r="CY89" s="41"/>
+      <c r="CZ89" s="41"/>
+      <c r="DA89" s="41"/>
+      <c r="DB89" s="41"/>
+      <c r="DC89" s="41"/>
+      <c r="DD89" s="41"/>
+      <c r="DE89" s="41"/>
+      <c r="DF89" s="41"/>
+      <c r="DG89" s="41"/>
+      <c r="DH89" s="41"/>
+      <c r="DI89" s="41"/>
+      <c r="DJ89" s="41"/>
+      <c r="DK89" s="41"/>
+      <c r="DL89" s="41"/>
+      <c r="DM89" s="41"/>
+      <c r="DN89" s="41"/>
+      <c r="DO89" s="41"/>
+      <c r="DP89" s="41"/>
+      <c r="DQ89" s="41"/>
+      <c r="DR89" s="41"/>
+      <c r="DS89" s="41"/>
+      <c r="DT89" s="41"/>
+      <c r="DU89" s="41"/>
+      <c r="DV89" s="41"/>
+      <c r="DW89" s="41"/>
+      <c r="DX89" s="41"/>
+      <c r="DY89" s="41"/>
+      <c r="DZ89" s="41"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="15" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B90" s="15" t="n">
         <f aca="false">+B92+B93-B109-B110</f>
@@ -21716,7 +21849,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B93" s="3" t="n">
         <v>1962</v>
@@ -21793,7 +21926,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B94" s="3" t="n">
         <v>1685</v>
@@ -21914,7 +22047,7 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B95" s="3" t="n">
         <v>1090</v>
@@ -21988,47 +22121,47 @@
       <c r="AF95" s="3" t="n">
         <v>1224</v>
       </c>
-      <c r="AG95" s="60" t="n">
+      <c r="AG95" s="64" t="n">
         <f aca="false">+AG23*0.05</f>
         <v>1325.12175</v>
       </c>
-      <c r="AH95" s="60" t="n">
+      <c r="AH95" s="64" t="n">
         <f aca="false">+AH23*0.05</f>
         <v>1464.25953375</v>
       </c>
-      <c r="AI95" s="60" t="n">
+      <c r="AI95" s="64" t="n">
         <f aca="false">+AI23*0.05</f>
         <v>1603.36418945625</v>
       </c>
-      <c r="AJ95" s="60" t="n">
+      <c r="AJ95" s="64" t="n">
         <f aca="false">+AJ23*0.05</f>
         <v>1747.66696650732</v>
       </c>
-      <c r="AK95" s="60" t="n">
+      <c r="AK95" s="64" t="n">
         <f aca="false">+AK23*0.05</f>
         <v>1887.4803238279</v>
       </c>
-      <c r="AL95" s="60" t="n">
+      <c r="AL95" s="64" t="n">
         <f aca="false">+AL23*0.05</f>
         <v>2019.60394649585</v>
       </c>
-      <c r="AM95" s="60" t="n">
+      <c r="AM95" s="64" t="n">
         <f aca="false">+AM23*0.05</f>
         <v>2140.7801832856</v>
       </c>
-      <c r="AN95" s="60" t="n">
+      <c r="AN95" s="64" t="n">
         <f aca="false">+AN23*0.05</f>
         <v>2247.81919244988</v>
       </c>
-      <c r="AO95" s="60" t="n">
+      <c r="AO95" s="64" t="n">
         <f aca="false">+AO23*0.05</f>
         <v>2337.73196014788</v>
       </c>
-      <c r="AP95" s="60" t="n">
+      <c r="AP95" s="64" t="n">
         <f aca="false">+AP23*0.05</f>
         <v>2407.86391895231</v>
       </c>
-      <c r="AQ95" s="60" t="n">
+      <c r="AQ95" s="64" t="n">
         <f aca="false">+AQ23*0.05</f>
         <v>2456.02119733136</v>
       </c>
@@ -22177,7 +22310,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B97" s="3" t="n">
         <v>1703</v>
@@ -22254,7 +22387,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B98" s="3" t="n">
         <v>435</v>
@@ -22331,7 +22464,7 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B99" s="3" t="n">
         <v>12795</v>
@@ -22408,7 +22541,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B100" s="3" t="n">
         <v>1743</v>
@@ -22485,7 +22618,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B101" s="3" t="n">
         <v>950</v>
@@ -22560,9 +22693,9 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="102" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B102" s="3" t="n">
         <v>874</v>
@@ -22742,9 +22875,9 @@
       <c r="DY102" s="3"/>
       <c r="DZ102" s="3"/>
     </row>
-    <row r="103" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B103" s="3" t="n">
         <f aca="false">SUM(B92:B102)</f>
@@ -22954,7 +23087,7 @@
       <c r="DY103" s="3"/>
       <c r="DZ103" s="3"/>
     </row>
-    <row r="104" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -23086,7 +23219,7 @@
       <c r="DY104" s="3"/>
       <c r="DZ104" s="3"/>
     </row>
-    <row r="105" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -23218,9 +23351,9 @@
       <c r="DY105" s="3"/>
       <c r="DZ105" s="3"/>
     </row>
-    <row r="106" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B106" s="3" t="n">
         <v>295</v>
@@ -23433,9 +23566,9 @@
       <c r="DY106" s="3"/>
       <c r="DZ106" s="3"/>
     </row>
-    <row r="107" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B107" s="3" t="n">
         <v>1333</v>
@@ -23516,47 +23649,47 @@
       <c r="AF107" s="3" t="n">
         <v>2648</v>
       </c>
-      <c r="AG107" s="60" t="n">
+      <c r="AG107" s="64" t="n">
         <f aca="false">+AG23*0.1</f>
         <v>2650.2435</v>
       </c>
-      <c r="AH107" s="60" t="n">
+      <c r="AH107" s="64" t="n">
         <f aca="false">+AH23*0.1</f>
         <v>2928.5190675</v>
       </c>
-      <c r="AI107" s="60" t="n">
+      <c r="AI107" s="64" t="n">
         <f aca="false">+AI23*0.1</f>
         <v>3206.7283789125</v>
       </c>
-      <c r="AJ107" s="60" t="n">
+      <c r="AJ107" s="64" t="n">
         <f aca="false">+AJ23*0.09</f>
         <v>3145.80053971317</v>
       </c>
-      <c r="AK107" s="60" t="n">
+      <c r="AK107" s="64" t="n">
         <f aca="false">+AK23*0.09</f>
         <v>3397.46458289022</v>
       </c>
-      <c r="AL107" s="60" t="n">
+      <c r="AL107" s="64" t="n">
         <f aca="false">+AL23*0.09</f>
         <v>3635.28710369253</v>
       </c>
-      <c r="AM107" s="60" t="n">
+      <c r="AM107" s="64" t="n">
         <f aca="false">+AM23*0.09</f>
         <v>3853.40432991408</v>
       </c>
-      <c r="AN107" s="60" t="n">
+      <c r="AN107" s="64" t="n">
         <f aca="false">+AN23*0.08</f>
         <v>3596.51070791981</v>
       </c>
-      <c r="AO107" s="60" t="n">
+      <c r="AO107" s="64" t="n">
         <f aca="false">+AO23*0.08</f>
         <v>3740.3711362366</v>
       </c>
-      <c r="AP107" s="60" t="n">
+      <c r="AP107" s="64" t="n">
         <f aca="false">+AP23*0.08</f>
         <v>3852.5822703237</v>
       </c>
-      <c r="AQ107" s="60" t="n">
+      <c r="AQ107" s="64" t="n">
         <f aca="false">+AQ23*0.08</f>
         <v>3929.63391573018</v>
       </c>
@@ -23648,7 +23781,7 @@
       <c r="DY107" s="3"/>
       <c r="DZ107" s="3"/>
     </row>
-    <row r="108" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3"/>
       <c r="B108" s="25" t="n">
         <f aca="false">+B107/B$23</f>
@@ -23885,7 +24018,7 @@
       <c r="DY108" s="3"/>
       <c r="DZ108" s="3"/>
     </row>
-    <row r="109" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
         <v>6</v>
       </c>
@@ -24084,9 +24217,9 @@
       <c r="DY109" s="3"/>
       <c r="DZ109" s="3"/>
     </row>
-    <row r="110" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B110" s="3" t="n">
         <v>3626</v>
@@ -24266,9 +24399,9 @@
       <c r="DY110" s="3"/>
       <c r="DZ110" s="3"/>
     </row>
-    <row r="111" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B111" s="3" t="n">
         <f aca="false">+4894+125</f>
@@ -24472,9 +24605,9 @@
       <c r="DY111" s="3"/>
       <c r="DZ111" s="3"/>
     </row>
-    <row r="112" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B112" s="3" t="n">
         <f aca="false">+83+540</f>
@@ -24678,9 +24811,9 @@
       <c r="DY112" s="3"/>
       <c r="DZ112" s="3"/>
     </row>
-    <row r="113" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B113" s="3" t="n">
         <f aca="false">+93+4</f>
@@ -24884,9 +25017,9 @@
       <c r="DY113" s="3"/>
       <c r="DZ113" s="3"/>
     </row>
-    <row r="114" s="61" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B114" s="3" t="n">
         <f aca="false">+447+262</f>
@@ -25071,9 +25204,9 @@
       <c r="DY114" s="3"/>
       <c r="DZ114" s="3"/>
     </row>
-    <row r="115" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" s="65" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B115" s="3" t="n">
         <f aca="false">SUM(B106:B114)</f>
@@ -25283,9 +25416,9 @@
       <c r="DY115" s="3"/>
       <c r="DZ115" s="3"/>
     </row>
-    <row r="116" s="62" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="65" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B116" s="3" t="n">
         <v>0</v>
@@ -25467,7 +25600,7 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B117" s="3" t="n">
         <v>0</v>
@@ -25544,7 +25677,7 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B118" s="3" t="n">
         <v>8750</v>
@@ -25621,7 +25754,7 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B119" s="3" t="n">
         <v>24961</v>
@@ -25698,7 +25831,7 @@
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B120" s="3" t="n">
         <v>-177</v>
@@ -25775,7 +25908,7 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B121" s="3" t="n">
         <v>-19759</v>
@@ -25852,7 +25985,7 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B122" s="3" t="n">
         <f aca="false">SUM(B116:B121)</f>
@@ -25961,7 +26094,7 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B123" s="3" t="n">
         <f aca="false">+B122+B115</f>
@@ -26070,7 +26203,7 @@
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B126" s="3" t="n">
         <f aca="false">B57</f>
@@ -26225,7 +26358,7 @@
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B127" s="3" t="n">
         <v>1266</v>
@@ -26306,7 +26439,7 @@
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B128" s="3" t="n">
         <v>213</v>
@@ -26384,47 +26517,47 @@
         <f aca="false">SUM(N128:Q128)</f>
         <v>818</v>
       </c>
-      <c r="AG128" s="63" t="n">
+      <c r="AG128" s="66" t="n">
         <f aca="false">+AG23*0.035</f>
         <v>927.585225</v>
       </c>
-      <c r="AH128" s="63" t="n">
+      <c r="AH128" s="66" t="n">
         <f aca="false">+AH23*0.035</f>
         <v>1024.981673625</v>
       </c>
-      <c r="AI128" s="63" t="n">
+      <c r="AI128" s="66" t="n">
         <f aca="false">+AI23*0.035</f>
         <v>1122.35493261938</v>
       </c>
-      <c r="AJ128" s="63" t="n">
+      <c r="AJ128" s="66" t="n">
         <f aca="false">+AJ23*0.035</f>
         <v>1223.36687655512</v>
       </c>
-      <c r="AK128" s="63" t="n">
+      <c r="AK128" s="66" t="n">
         <f aca="false">+AK23*0.035</f>
         <v>1321.23622667953</v>
       </c>
-      <c r="AL128" s="63" t="n">
+      <c r="AL128" s="66" t="n">
         <f aca="false">+AL23*0.035</f>
         <v>1413.7227625471</v>
       </c>
-      <c r="AM128" s="63" t="n">
+      <c r="AM128" s="66" t="n">
         <f aca="false">+AM23*0.035</f>
         <v>1498.54612829992</v>
       </c>
-      <c r="AN128" s="63" t="n">
+      <c r="AN128" s="66" t="n">
         <f aca="false">+AN23*0.035</f>
         <v>1573.47343471492</v>
       </c>
-      <c r="AO128" s="63" t="n">
+      <c r="AO128" s="66" t="n">
         <f aca="false">+AO23*0.035</f>
         <v>1636.41237210351</v>
       </c>
-      <c r="AP128" s="63" t="n">
+      <c r="AP128" s="66" t="n">
         <f aca="false">+AP23*0.035</f>
         <v>1685.50474326662</v>
       </c>
-      <c r="AQ128" s="63" t="n">
+      <c r="AQ128" s="66" t="n">
         <f aca="false">+AQ23*0.035</f>
         <v>1719.21483813195</v>
       </c>
@@ -26656,7 +26789,7 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B130" s="3" t="n">
         <v>322</v>
@@ -26737,7 +26870,7 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B131" s="3" t="n">
         <v>17</v>
@@ -26818,7 +26951,7 @@
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B132" s="3" t="n">
         <v>153</v>
@@ -26901,7 +27034,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B133" s="3" t="n">
         <v>141</v>
@@ -26979,12 +27112,12 @@
         <f aca="false">SUM(N133:Q133)</f>
         <v>771</v>
       </c>
-      <c r="AR133" s="64"/>
-      <c r="AS133" s="64"/>
+      <c r="AR133" s="67"/>
+      <c r="AS133" s="67"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B134" s="3" t="n">
         <v>-343</v>
@@ -27065,7 +27198,7 @@
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B135" s="3" t="n">
         <f aca="false">SUM(B127:B134)</f>
@@ -27174,7 +27307,7 @@
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B137" s="3" t="n">
         <v>100</v>
@@ -27252,47 +27385,47 @@
         <f aca="false">SUM(N137:Q137)</f>
         <v>179</v>
       </c>
-      <c r="AG137" s="63" t="n">
+      <c r="AG137" s="66" t="n">
         <f aca="false">+AG23*0.007</f>
         <v>185.517045</v>
       </c>
-      <c r="AH137" s="63" t="n">
+      <c r="AH137" s="66" t="n">
         <f aca="false">+AH23*0.007</f>
         <v>204.996334725</v>
       </c>
-      <c r="AI137" s="63" t="n">
+      <c r="AI137" s="66" t="n">
         <f aca="false">+AI23*0.007</f>
         <v>224.470986523875</v>
       </c>
-      <c r="AJ137" s="63" t="n">
+      <c r="AJ137" s="66" t="n">
         <f aca="false">+AJ23*0.007</f>
         <v>244.673375311024</v>
       </c>
-      <c r="AK137" s="63" t="n">
+      <c r="AK137" s="66" t="n">
         <f aca="false">+AK23*0.007</f>
         <v>264.247245335906</v>
       </c>
-      <c r="AL137" s="63" t="n">
+      <c r="AL137" s="66" t="n">
         <f aca="false">+AL23*0.007</f>
         <v>282.744552509419</v>
       </c>
-      <c r="AM137" s="63" t="n">
+      <c r="AM137" s="66" t="n">
         <f aca="false">+AM23*0.007</f>
         <v>299.709225659984</v>
       </c>
-      <c r="AN137" s="63" t="n">
+      <c r="AN137" s="66" t="n">
         <f aca="false">+AN23*0.007</f>
         <v>314.694686942983</v>
       </c>
-      <c r="AO137" s="63" t="n">
+      <c r="AO137" s="66" t="n">
         <f aca="false">+AO23*0.007</f>
         <v>327.282474420703</v>
       </c>
-      <c r="AP137" s="63" t="n">
+      <c r="AP137" s="66" t="n">
         <f aca="false">+AP23*0.007</f>
         <v>337.100948653323</v>
       </c>
-      <c r="AQ137" s="63" t="n">
+      <c r="AQ137" s="66" t="n">
         <f aca="false">+AQ23*0.007</f>
         <v>343.84296762639</v>
       </c>
@@ -27524,7 +27657,7 @@
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="17" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B139" s="17" t="n">
         <f aca="false">+B135-B137</f>
@@ -27750,95 +27883,95 @@
       <c r="AQ140" s="25"/>
       <c r="AR140" s="25"/>
       <c r="AS140" s="25"/>
-      <c r="AT140" s="65"/>
-      <c r="AU140" s="65"/>
-      <c r="AV140" s="65"/>
-      <c r="AW140" s="65"/>
-      <c r="AX140" s="65"/>
-      <c r="AY140" s="65"/>
-      <c r="AZ140" s="65"/>
-      <c r="BA140" s="65"/>
-      <c r="BB140" s="65"/>
-      <c r="BC140" s="65"/>
-      <c r="BD140" s="65"/>
-      <c r="BE140" s="65"/>
-      <c r="BF140" s="65"/>
-      <c r="BG140" s="65"/>
-      <c r="BH140" s="65"/>
-      <c r="BI140" s="65"/>
-      <c r="BJ140" s="65"/>
-      <c r="BK140" s="65"/>
-      <c r="BL140" s="65"/>
-      <c r="BM140" s="65"/>
-      <c r="BN140" s="65"/>
-      <c r="BO140" s="65"/>
-      <c r="BP140" s="65"/>
-      <c r="BQ140" s="65"/>
-      <c r="BR140" s="65"/>
-      <c r="BS140" s="65"/>
-      <c r="BT140" s="65"/>
-      <c r="BU140" s="65"/>
-      <c r="BV140" s="65"/>
-      <c r="BW140" s="65"/>
-      <c r="BX140" s="65"/>
-      <c r="BY140" s="65"/>
-      <c r="BZ140" s="65"/>
-      <c r="CA140" s="65"/>
-      <c r="CB140" s="65"/>
-      <c r="CC140" s="65"/>
-      <c r="CD140" s="65"/>
-      <c r="CE140" s="65"/>
-      <c r="CF140" s="65"/>
-      <c r="CG140" s="65"/>
-      <c r="CH140" s="65"/>
-      <c r="CI140" s="65"/>
-      <c r="CJ140" s="65"/>
-      <c r="CK140" s="65"/>
-      <c r="CL140" s="65"/>
-      <c r="CM140" s="65"/>
-      <c r="CN140" s="65"/>
-      <c r="CO140" s="65"/>
-      <c r="CP140" s="65"/>
-      <c r="CQ140" s="65"/>
-      <c r="CR140" s="65"/>
-      <c r="CS140" s="65"/>
-      <c r="CT140" s="65"/>
-      <c r="CU140" s="65"/>
-      <c r="CV140" s="65"/>
-      <c r="CW140" s="65"/>
-      <c r="CX140" s="65"/>
-      <c r="CY140" s="65"/>
-      <c r="CZ140" s="65"/>
-      <c r="DA140" s="65"/>
-      <c r="DB140" s="65"/>
-      <c r="DC140" s="65"/>
-      <c r="DD140" s="65"/>
-      <c r="DE140" s="65"/>
-      <c r="DF140" s="65"/>
-      <c r="DG140" s="65"/>
-      <c r="DH140" s="65"/>
-      <c r="DI140" s="65"/>
-      <c r="DJ140" s="65"/>
-      <c r="DK140" s="65"/>
-      <c r="DL140" s="65"/>
-      <c r="DM140" s="65"/>
-      <c r="DN140" s="65"/>
-      <c r="DO140" s="65"/>
-      <c r="DP140" s="65"/>
-      <c r="DQ140" s="65"/>
-      <c r="DR140" s="65"/>
-      <c r="DS140" s="65"/>
-      <c r="DT140" s="65"/>
-      <c r="DU140" s="65"/>
-      <c r="DV140" s="65"/>
-      <c r="DW140" s="65"/>
-      <c r="DX140" s="65"/>
-      <c r="DY140" s="65"/>
-      <c r="DZ140" s="65"/>
+      <c r="AT140" s="68"/>
+      <c r="AU140" s="68"/>
+      <c r="AV140" s="68"/>
+      <c r="AW140" s="68"/>
+      <c r="AX140" s="68"/>
+      <c r="AY140" s="68"/>
+      <c r="AZ140" s="68"/>
+      <c r="BA140" s="68"/>
+      <c r="BB140" s="68"/>
+      <c r="BC140" s="68"/>
+      <c r="BD140" s="68"/>
+      <c r="BE140" s="68"/>
+      <c r="BF140" s="68"/>
+      <c r="BG140" s="68"/>
+      <c r="BH140" s="68"/>
+      <c r="BI140" s="68"/>
+      <c r="BJ140" s="68"/>
+      <c r="BK140" s="68"/>
+      <c r="BL140" s="68"/>
+      <c r="BM140" s="68"/>
+      <c r="BN140" s="68"/>
+      <c r="BO140" s="68"/>
+      <c r="BP140" s="68"/>
+      <c r="BQ140" s="68"/>
+      <c r="BR140" s="68"/>
+      <c r="BS140" s="68"/>
+      <c r="BT140" s="68"/>
+      <c r="BU140" s="68"/>
+      <c r="BV140" s="68"/>
+      <c r="BW140" s="68"/>
+      <c r="BX140" s="68"/>
+      <c r="BY140" s="68"/>
+      <c r="BZ140" s="68"/>
+      <c r="CA140" s="68"/>
+      <c r="CB140" s="68"/>
+      <c r="CC140" s="68"/>
+      <c r="CD140" s="68"/>
+      <c r="CE140" s="68"/>
+      <c r="CF140" s="68"/>
+      <c r="CG140" s="68"/>
+      <c r="CH140" s="68"/>
+      <c r="CI140" s="68"/>
+      <c r="CJ140" s="68"/>
+      <c r="CK140" s="68"/>
+      <c r="CL140" s="68"/>
+      <c r="CM140" s="68"/>
+      <c r="CN140" s="68"/>
+      <c r="CO140" s="68"/>
+      <c r="CP140" s="68"/>
+      <c r="CQ140" s="68"/>
+      <c r="CR140" s="68"/>
+      <c r="CS140" s="68"/>
+      <c r="CT140" s="68"/>
+      <c r="CU140" s="68"/>
+      <c r="CV140" s="68"/>
+      <c r="CW140" s="68"/>
+      <c r="CX140" s="68"/>
+      <c r="CY140" s="68"/>
+      <c r="CZ140" s="68"/>
+      <c r="DA140" s="68"/>
+      <c r="DB140" s="68"/>
+      <c r="DC140" s="68"/>
+      <c r="DD140" s="68"/>
+      <c r="DE140" s="68"/>
+      <c r="DF140" s="68"/>
+      <c r="DG140" s="68"/>
+      <c r="DH140" s="68"/>
+      <c r="DI140" s="68"/>
+      <c r="DJ140" s="68"/>
+      <c r="DK140" s="68"/>
+      <c r="DL140" s="68"/>
+      <c r="DM140" s="68"/>
+      <c r="DN140" s="68"/>
+      <c r="DO140" s="68"/>
+      <c r="DP140" s="68"/>
+      <c r="DQ140" s="68"/>
+      <c r="DR140" s="68"/>
+      <c r="DS140" s="68"/>
+      <c r="DT140" s="68"/>
+      <c r="DU140" s="68"/>
+      <c r="DV140" s="68"/>
+      <c r="DW140" s="68"/>
+      <c r="DX140" s="68"/>
+      <c r="DY140" s="68"/>
+      <c r="DZ140" s="68"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AR141" s="61"/>
-      <c r="AS141" s="61"/>
+      <c r="AR141" s="62"/>
+      <c r="AS141" s="62"/>
       <c r="AT141" s="17"/>
       <c r="AU141" s="17"/>
       <c r="AV141" s="17"/>
@@ -27927,7 +28060,7 @@
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>22516</v>
@@ -27947,95 +28080,95 @@
       <c r="AF142" s="3" t="n">
         <v>31360</v>
       </c>
-      <c r="AT142" s="61"/>
-      <c r="AU142" s="61"/>
-      <c r="AV142" s="61"/>
-      <c r="AW142" s="61"/>
-      <c r="AX142" s="61"/>
-      <c r="AY142" s="61"/>
-      <c r="AZ142" s="61"/>
-      <c r="BA142" s="61"/>
-      <c r="BB142" s="61"/>
-      <c r="BC142" s="61"/>
-      <c r="BD142" s="61"/>
-      <c r="BE142" s="61"/>
-      <c r="BF142" s="61"/>
-      <c r="BG142" s="61"/>
-      <c r="BH142" s="61"/>
-      <c r="BI142" s="61"/>
-      <c r="BJ142" s="61"/>
-      <c r="BK142" s="61"/>
-      <c r="BL142" s="61"/>
-      <c r="BM142" s="61"/>
-      <c r="BN142" s="61"/>
-      <c r="BO142" s="61"/>
-      <c r="BP142" s="61"/>
-      <c r="BQ142" s="61"/>
-      <c r="BR142" s="61"/>
-      <c r="BS142" s="61"/>
-      <c r="BT142" s="61"/>
-      <c r="BU142" s="61"/>
-      <c r="BV142" s="61"/>
-      <c r="BW142" s="61"/>
-      <c r="BX142" s="61"/>
-      <c r="BY142" s="61"/>
-      <c r="BZ142" s="61"/>
-      <c r="CA142" s="61"/>
-      <c r="CB142" s="61"/>
-      <c r="CC142" s="61"/>
-      <c r="CD142" s="61"/>
-      <c r="CE142" s="61"/>
-      <c r="CF142" s="61"/>
-      <c r="CG142" s="61"/>
-      <c r="CH142" s="61"/>
-      <c r="CI142" s="61"/>
-      <c r="CJ142" s="61"/>
-      <c r="CK142" s="61"/>
-      <c r="CL142" s="61"/>
-      <c r="CM142" s="61"/>
-      <c r="CN142" s="61"/>
-      <c r="CO142" s="61"/>
-      <c r="CP142" s="61"/>
-      <c r="CQ142" s="61"/>
-      <c r="CR142" s="61"/>
-      <c r="CS142" s="61"/>
-      <c r="CT142" s="61"/>
-      <c r="CU142" s="61"/>
-      <c r="CV142" s="61"/>
-      <c r="CW142" s="61"/>
-      <c r="CX142" s="61"/>
-      <c r="CY142" s="61"/>
-      <c r="CZ142" s="61"/>
-      <c r="DA142" s="61"/>
-      <c r="DB142" s="61"/>
-      <c r="DC142" s="61"/>
-      <c r="DD142" s="61"/>
-      <c r="DE142" s="61"/>
-      <c r="DF142" s="61"/>
-      <c r="DG142" s="61"/>
-      <c r="DH142" s="61"/>
-      <c r="DI142" s="61"/>
-      <c r="DJ142" s="61"/>
-      <c r="DK142" s="61"/>
-      <c r="DL142" s="61"/>
-      <c r="DM142" s="61"/>
-      <c r="DN142" s="61"/>
-      <c r="DO142" s="61"/>
-      <c r="DP142" s="61"/>
-      <c r="DQ142" s="61"/>
-      <c r="DR142" s="61"/>
-      <c r="DS142" s="61"/>
-      <c r="DT142" s="61"/>
-      <c r="DU142" s="61"/>
-      <c r="DV142" s="61"/>
-      <c r="DW142" s="61"/>
-      <c r="DX142" s="61"/>
-      <c r="DY142" s="61"/>
-      <c r="DZ142" s="61"/>
+      <c r="AT142" s="62"/>
+      <c r="AU142" s="62"/>
+      <c r="AV142" s="62"/>
+      <c r="AW142" s="62"/>
+      <c r="AX142" s="62"/>
+      <c r="AY142" s="62"/>
+      <c r="AZ142" s="62"/>
+      <c r="BA142" s="62"/>
+      <c r="BB142" s="62"/>
+      <c r="BC142" s="62"/>
+      <c r="BD142" s="62"/>
+      <c r="BE142" s="62"/>
+      <c r="BF142" s="62"/>
+      <c r="BG142" s="62"/>
+      <c r="BH142" s="62"/>
+      <c r="BI142" s="62"/>
+      <c r="BJ142" s="62"/>
+      <c r="BK142" s="62"/>
+      <c r="BL142" s="62"/>
+      <c r="BM142" s="62"/>
+      <c r="BN142" s="62"/>
+      <c r="BO142" s="62"/>
+      <c r="BP142" s="62"/>
+      <c r="BQ142" s="62"/>
+      <c r="BR142" s="62"/>
+      <c r="BS142" s="62"/>
+      <c r="BT142" s="62"/>
+      <c r="BU142" s="62"/>
+      <c r="BV142" s="62"/>
+      <c r="BW142" s="62"/>
+      <c r="BX142" s="62"/>
+      <c r="BY142" s="62"/>
+      <c r="BZ142" s="62"/>
+      <c r="CA142" s="62"/>
+      <c r="CB142" s="62"/>
+      <c r="CC142" s="62"/>
+      <c r="CD142" s="62"/>
+      <c r="CE142" s="62"/>
+      <c r="CF142" s="62"/>
+      <c r="CG142" s="62"/>
+      <c r="CH142" s="62"/>
+      <c r="CI142" s="62"/>
+      <c r="CJ142" s="62"/>
+      <c r="CK142" s="62"/>
+      <c r="CL142" s="62"/>
+      <c r="CM142" s="62"/>
+      <c r="CN142" s="62"/>
+      <c r="CO142" s="62"/>
+      <c r="CP142" s="62"/>
+      <c r="CQ142" s="62"/>
+      <c r="CR142" s="62"/>
+      <c r="CS142" s="62"/>
+      <c r="CT142" s="62"/>
+      <c r="CU142" s="62"/>
+      <c r="CV142" s="62"/>
+      <c r="CW142" s="62"/>
+      <c r="CX142" s="62"/>
+      <c r="CY142" s="62"/>
+      <c r="CZ142" s="62"/>
+      <c r="DA142" s="62"/>
+      <c r="DB142" s="62"/>
+      <c r="DC142" s="62"/>
+      <c r="DD142" s="62"/>
+      <c r="DE142" s="62"/>
+      <c r="DF142" s="62"/>
+      <c r="DG142" s="62"/>
+      <c r="DH142" s="62"/>
+      <c r="DI142" s="62"/>
+      <c r="DJ142" s="62"/>
+      <c r="DK142" s="62"/>
+      <c r="DL142" s="62"/>
+      <c r="DM142" s="62"/>
+      <c r="DN142" s="62"/>
+      <c r="DO142" s="62"/>
+      <c r="DP142" s="62"/>
+      <c r="DQ142" s="62"/>
+      <c r="DR142" s="62"/>
+      <c r="DS142" s="62"/>
+      <c r="DT142" s="62"/>
+      <c r="DU142" s="62"/>
+      <c r="DV142" s="62"/>
+      <c r="DW142" s="62"/>
+      <c r="DX142" s="62"/>
+      <c r="DY142" s="62"/>
+      <c r="DZ142" s="62"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="AA143" s="3" t="n">
         <f aca="false">+(AA23*1000000)/AA142</f>
@@ -28064,7 +28197,7 @@
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B145" s="3" t="n">
         <v>13830</v>
@@ -28322,7 +28455,7 @@
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C148" s="3" t="n">
         <f aca="false">+AVERAGE(B94:C94)/C23*90</f>
@@ -28412,134 +28545,134 @@
         <f aca="false">+AVERAGE(AE94:AF94)/AF23*365</f>
         <v>33.9063486053263</v>
       </c>
-      <c r="AG148" s="63" t="n">
+      <c r="AG148" s="66" t="n">
         <f aca="false">+AF148-1</f>
         <v>32.9063486053263</v>
       </c>
-      <c r="AH148" s="63" t="n">
+      <c r="AH148" s="66" t="n">
         <v>33</v>
       </c>
-      <c r="AI148" s="63" t="n">
+      <c r="AI148" s="66" t="n">
         <f aca="false">+AH148-1</f>
         <v>32</v>
       </c>
-      <c r="AJ148" s="63" t="n">
+      <c r="AJ148" s="66" t="n">
         <v>32</v>
       </c>
-      <c r="AK148" s="63" t="n">
+      <c r="AK148" s="66" t="n">
         <f aca="false">+AJ148-1</f>
         <v>31</v>
       </c>
-      <c r="AL148" s="63" t="n">
+      <c r="AL148" s="66" t="n">
         <v>31</v>
       </c>
-      <c r="AM148" s="63" t="n">
+      <c r="AM148" s="66" t="n">
         <f aca="false">+AL148-1</f>
         <v>30</v>
       </c>
-      <c r="AN148" s="63" t="n">
+      <c r="AN148" s="66" t="n">
         <v>30</v>
       </c>
-      <c r="AO148" s="63" t="n">
+      <c r="AO148" s="66" t="n">
         <f aca="false">+AN148-1</f>
         <v>29</v>
       </c>
-      <c r="AP148" s="63" t="n">
+      <c r="AP148" s="66" t="n">
         <v>29</v>
       </c>
-      <c r="AQ148" s="63" t="n">
+      <c r="AQ148" s="66" t="n">
         <f aca="false">+AP148-1</f>
         <v>28</v>
       </c>
-      <c r="AT148" s="64"/>
-      <c r="AU148" s="64"/>
-      <c r="AV148" s="64"/>
-      <c r="AW148" s="64"/>
-      <c r="AX148" s="64"/>
-      <c r="AY148" s="64"/>
-      <c r="AZ148" s="64"/>
-      <c r="BA148" s="64"/>
-      <c r="BB148" s="64"/>
-      <c r="BC148" s="64"/>
-      <c r="BD148" s="64"/>
-      <c r="BE148" s="64"/>
-      <c r="BF148" s="64"/>
-      <c r="BG148" s="64"/>
-      <c r="BH148" s="64"/>
-      <c r="BI148" s="64"/>
-      <c r="BJ148" s="64"/>
-      <c r="BK148" s="64"/>
-      <c r="BL148" s="64"/>
-      <c r="BM148" s="64"/>
-      <c r="BN148" s="64"/>
-      <c r="BO148" s="64"/>
-      <c r="BP148" s="64"/>
-      <c r="BQ148" s="64"/>
-      <c r="BR148" s="64"/>
-      <c r="BS148" s="64"/>
-      <c r="BT148" s="64"/>
-      <c r="BU148" s="64"/>
-      <c r="BV148" s="64"/>
-      <c r="BW148" s="64"/>
-      <c r="BX148" s="64"/>
-      <c r="BY148" s="64"/>
-      <c r="BZ148" s="64"/>
-      <c r="CA148" s="64"/>
-      <c r="CB148" s="64"/>
-      <c r="CC148" s="64"/>
-      <c r="CD148" s="64"/>
-      <c r="CE148" s="64"/>
-      <c r="CF148" s="64"/>
-      <c r="CG148" s="64"/>
-      <c r="CH148" s="64"/>
-      <c r="CI148" s="64"/>
-      <c r="CJ148" s="64"/>
-      <c r="CK148" s="64"/>
-      <c r="CL148" s="64"/>
-      <c r="CM148" s="64"/>
-      <c r="CN148" s="64"/>
-      <c r="CO148" s="64"/>
-      <c r="CP148" s="64"/>
-      <c r="CQ148" s="64"/>
-      <c r="CR148" s="64"/>
-      <c r="CS148" s="64"/>
-      <c r="CT148" s="64"/>
-      <c r="CU148" s="64"/>
-      <c r="CV148" s="64"/>
-      <c r="CW148" s="64"/>
-      <c r="CX148" s="64"/>
-      <c r="CY148" s="64"/>
-      <c r="CZ148" s="64"/>
-      <c r="DA148" s="64"/>
-      <c r="DB148" s="64"/>
-      <c r="DC148" s="64"/>
-      <c r="DD148" s="64"/>
-      <c r="DE148" s="64"/>
-      <c r="DF148" s="64"/>
-      <c r="DG148" s="64"/>
-      <c r="DH148" s="64"/>
-      <c r="DI148" s="64"/>
-      <c r="DJ148" s="64"/>
-      <c r="DK148" s="64"/>
-      <c r="DL148" s="64"/>
-      <c r="DM148" s="64"/>
-      <c r="DN148" s="64"/>
-      <c r="DO148" s="64"/>
-      <c r="DP148" s="64"/>
-      <c r="DQ148" s="64"/>
-      <c r="DR148" s="64"/>
-      <c r="DS148" s="64"/>
-      <c r="DT148" s="64"/>
-      <c r="DU148" s="64"/>
-      <c r="DV148" s="64"/>
-      <c r="DW148" s="64"/>
-      <c r="DX148" s="64"/>
-      <c r="DY148" s="64"/>
-      <c r="DZ148" s="64"/>
+      <c r="AT148" s="67"/>
+      <c r="AU148" s="67"/>
+      <c r="AV148" s="67"/>
+      <c r="AW148" s="67"/>
+      <c r="AX148" s="67"/>
+      <c r="AY148" s="67"/>
+      <c r="AZ148" s="67"/>
+      <c r="BA148" s="67"/>
+      <c r="BB148" s="67"/>
+      <c r="BC148" s="67"/>
+      <c r="BD148" s="67"/>
+      <c r="BE148" s="67"/>
+      <c r="BF148" s="67"/>
+      <c r="BG148" s="67"/>
+      <c r="BH148" s="67"/>
+      <c r="BI148" s="67"/>
+      <c r="BJ148" s="67"/>
+      <c r="BK148" s="67"/>
+      <c r="BL148" s="67"/>
+      <c r="BM148" s="67"/>
+      <c r="BN148" s="67"/>
+      <c r="BO148" s="67"/>
+      <c r="BP148" s="67"/>
+      <c r="BQ148" s="67"/>
+      <c r="BR148" s="67"/>
+      <c r="BS148" s="67"/>
+      <c r="BT148" s="67"/>
+      <c r="BU148" s="67"/>
+      <c r="BV148" s="67"/>
+      <c r="BW148" s="67"/>
+      <c r="BX148" s="67"/>
+      <c r="BY148" s="67"/>
+      <c r="BZ148" s="67"/>
+      <c r="CA148" s="67"/>
+      <c r="CB148" s="67"/>
+      <c r="CC148" s="67"/>
+      <c r="CD148" s="67"/>
+      <c r="CE148" s="67"/>
+      <c r="CF148" s="67"/>
+      <c r="CG148" s="67"/>
+      <c r="CH148" s="67"/>
+      <c r="CI148" s="67"/>
+      <c r="CJ148" s="67"/>
+      <c r="CK148" s="67"/>
+      <c r="CL148" s="67"/>
+      <c r="CM148" s="67"/>
+      <c r="CN148" s="67"/>
+      <c r="CO148" s="67"/>
+      <c r="CP148" s="67"/>
+      <c r="CQ148" s="67"/>
+      <c r="CR148" s="67"/>
+      <c r="CS148" s="67"/>
+      <c r="CT148" s="67"/>
+      <c r="CU148" s="67"/>
+      <c r="CV148" s="67"/>
+      <c r="CW148" s="67"/>
+      <c r="CX148" s="67"/>
+      <c r="CY148" s="67"/>
+      <c r="CZ148" s="67"/>
+      <c r="DA148" s="67"/>
+      <c r="DB148" s="67"/>
+      <c r="DC148" s="67"/>
+      <c r="DD148" s="67"/>
+      <c r="DE148" s="67"/>
+      <c r="DF148" s="67"/>
+      <c r="DG148" s="67"/>
+      <c r="DH148" s="67"/>
+      <c r="DI148" s="67"/>
+      <c r="DJ148" s="67"/>
+      <c r="DK148" s="67"/>
+      <c r="DL148" s="67"/>
+      <c r="DM148" s="67"/>
+      <c r="DN148" s="67"/>
+      <c r="DO148" s="67"/>
+      <c r="DP148" s="67"/>
+      <c r="DQ148" s="67"/>
+      <c r="DR148" s="67"/>
+      <c r="DS148" s="67"/>
+      <c r="DT148" s="67"/>
+      <c r="DU148" s="67"/>
+      <c r="DV148" s="67"/>
+      <c r="DW148" s="67"/>
+      <c r="DX148" s="67"/>
+      <c r="DY148" s="67"/>
+      <c r="DZ148" s="67"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C149" s="3" t="n">
         <f aca="false">+AVERAGE(B106:C106)/C31*90</f>
@@ -28629,54 +28762,54 @@
         <f aca="false">+AVERAGE(AE106:AF106)/AF31*365</f>
         <v>52.4307790024701</v>
       </c>
-      <c r="AG149" s="63" t="n">
+      <c r="AG149" s="66" t="n">
         <f aca="false">+AF149+1</f>
         <v>53.4307790024701</v>
       </c>
-      <c r="AH149" s="63" t="n">
+      <c r="AH149" s="66" t="n">
         <f aca="false">+AG149+1</f>
         <v>54.4307790024701</v>
       </c>
-      <c r="AI149" s="63" t="n">
+      <c r="AI149" s="66" t="n">
         <f aca="false">+AH149+1</f>
         <v>55.4307790024701</v>
       </c>
-      <c r="AJ149" s="63" t="n">
+      <c r="AJ149" s="66" t="n">
         <f aca="false">+AI149+1</f>
         <v>56.4307790024701</v>
       </c>
-      <c r="AK149" s="63" t="n">
+      <c r="AK149" s="66" t="n">
         <f aca="false">+AJ149+1</f>
         <v>57.4307790024701</v>
       </c>
-      <c r="AL149" s="63" t="n">
+      <c r="AL149" s="66" t="n">
         <f aca="false">+AK149+1</f>
         <v>58.4307790024701</v>
       </c>
-      <c r="AM149" s="63" t="n">
+      <c r="AM149" s="66" t="n">
         <f aca="false">+AL149+1</f>
         <v>59.4307790024701</v>
       </c>
-      <c r="AN149" s="63" t="n">
+      <c r="AN149" s="66" t="n">
         <f aca="false">+AM149+1</f>
         <v>60.4307790024701</v>
       </c>
-      <c r="AO149" s="63" t="n">
+      <c r="AO149" s="66" t="n">
         <f aca="false">+AN149+1</f>
         <v>61.4307790024701</v>
       </c>
-      <c r="AP149" s="63" t="n">
+      <c r="AP149" s="66" t="n">
         <f aca="false">+AO149+1</f>
         <v>62.4307790024701</v>
       </c>
-      <c r="AQ149" s="63" t="n">
+      <c r="AQ149" s="66" t="n">
         <f aca="false">+AP149+1</f>
         <v>63.4307790024701</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C150" s="3" t="n">
         <f aca="false">+C148-C149</f>
@@ -28811,311 +28944,1215 @@
         <v>-35.4307790024701</v>
       </c>
     </row>
-    <row r="152" s="66" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G152" s="66" t="n">
+    <row r="152" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G152" s="69" t="n">
         <f aca="false">+G148/C148-1</f>
         <v>-0.0300183318056825</v>
       </c>
-      <c r="H152" s="66" t="n">
+      <c r="H152" s="69" t="n">
         <f aca="false">+H148/D148-1</f>
         <v>-0.031851564994667</v>
       </c>
-      <c r="I152" s="66" t="n">
+      <c r="I152" s="69" t="n">
         <f aca="false">+I148/E148-1</f>
         <v>-0.0356895346385367</v>
       </c>
-      <c r="J152" s="66" t="n">
+      <c r="J152" s="69" t="n">
         <f aca="false">+J148/F148-1</f>
         <v>-0.00526899492712707</v>
       </c>
-      <c r="K152" s="66" t="n">
+      <c r="K152" s="69" t="n">
         <f aca="false">+K148/G148-1</f>
         <v>0.0744624760106512</v>
       </c>
-      <c r="L152" s="66" t="n">
+      <c r="L152" s="69" t="n">
         <f aca="false">+L148/H148-1</f>
         <v>-0.00935161416637742</v>
       </c>
-      <c r="M152" s="66" t="n">
+      <c r="M152" s="69" t="n">
         <f aca="false">+M148/I148-1</f>
         <v>-0.143951725692673</v>
       </c>
-      <c r="N152" s="66" t="n">
+      <c r="N152" s="69" t="n">
         <f aca="false">+N148/J148-1</f>
         <v>-0.143099353052212</v>
       </c>
-      <c r="O152" s="66" t="n">
+      <c r="O152" s="69" t="n">
         <f aca="false">+O148/K148-1</f>
         <v>-0.188202766253999</v>
       </c>
-      <c r="P152" s="66" t="n">
+      <c r="P152" s="69" t="n">
         <f aca="false">+P148/L148-1</f>
         <v>-0.107584296108995</v>
       </c>
-      <c r="Q152" s="66" t="n">
+      <c r="Q152" s="69" t="n">
         <f aca="false">+Q148/M148-1</f>
         <v>0.0366011939877537</v>
       </c>
-      <c r="R152" s="66" t="n">
+      <c r="R152" s="69" t="n">
         <f aca="false">+R148/N148-1</f>
         <v>-0.0205799015529811</v>
       </c>
-      <c r="S152" s="66" t="n">
+      <c r="S152" s="69" t="n">
         <f aca="false">+S148/O148-1</f>
         <v>-0.0223451177413895</v>
       </c>
-      <c r="AC152" s="66" t="n">
+      <c r="AC152" s="69" t="n">
         <f aca="false">+AC148/AB148-1</f>
         <v>0.0791126228335133</v>
       </c>
-      <c r="AD152" s="66" t="n">
+      <c r="AD152" s="69" t="n">
         <f aca="false">+AD148/AC148-1</f>
         <v>-0.0132961866157912</v>
       </c>
-      <c r="AE152" s="66" t="n">
+      <c r="AE152" s="69" t="n">
         <f aca="false">+AE148/AD148-1</f>
         <v>-0.0959926956101073</v>
       </c>
-      <c r="AF152" s="66" t="n">
+      <c r="AF152" s="69" t="n">
         <f aca="false">+AF148/AE148-1</f>
         <v>-0.0699777725599569</v>
       </c>
-      <c r="AG152" s="66" t="n">
+      <c r="AG152" s="69" t="n">
         <f aca="false">+AG148/AF148-1</f>
         <v>-0.0294930017867778</v>
       </c>
-      <c r="AH152" s="66" t="n">
+      <c r="AH152" s="69" t="n">
         <f aca="false">+AH148/AG148-1</f>
         <v>0.00284599776769334</v>
       </c>
-      <c r="AI152" s="66" t="n">
+      <c r="AI152" s="69" t="n">
         <f aca="false">+AI148/AH148-1</f>
         <v>-0.0303030303030303</v>
       </c>
-      <c r="AJ152" s="66" t="n">
+      <c r="AJ152" s="69" t="n">
         <f aca="false">+AJ148/AI148-1</f>
         <v>0</v>
       </c>
-      <c r="AK152" s="66" t="n">
+      <c r="AK152" s="69" t="n">
         <f aca="false">+AK148/AJ148-1</f>
         <v>-0.03125</v>
       </c>
-      <c r="AL152" s="66" t="n">
+      <c r="AL152" s="69" t="n">
         <f aca="false">+AL148/AK148-1</f>
         <v>0</v>
       </c>
-      <c r="AM152" s="66" t="n">
+      <c r="AM152" s="69" t="n">
         <f aca="false">+AM148/AL148-1</f>
         <v>-0.032258064516129</v>
       </c>
-      <c r="AN152" s="66" t="n">
+      <c r="AN152" s="69" t="n">
         <f aca="false">+AN148/AM148-1</f>
         <v>0</v>
       </c>
-      <c r="AO152" s="66" t="n">
+      <c r="AO152" s="69" t="n">
         <f aca="false">+AO148/AN148-1</f>
         <v>-0.0333333333333333</v>
       </c>
-      <c r="AP152" s="66" t="n">
+      <c r="AP152" s="69" t="n">
         <f aca="false">+AP148/AO148-1</f>
         <v>0</v>
       </c>
-      <c r="AQ152" s="66" t="n">
+      <c r="AQ152" s="69" t="n">
         <f aca="false">+AQ148/AP148-1</f>
         <v>-0.0344827586206896</v>
       </c>
     </row>
-    <row r="153" s="66" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G153" s="66" t="n">
+    <row r="153" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G153" s="69" t="n">
         <f aca="false">+G149/C149-1</f>
         <v>0.0378732253470464</v>
       </c>
-      <c r="H153" s="66" t="n">
+      <c r="H153" s="69" t="n">
         <f aca="false">+H149/D149-1</f>
         <v>-0.0836012861736327</v>
       </c>
-      <c r="I153" s="66" t="n">
+      <c r="I153" s="69" t="n">
         <f aca="false">+I149/E149-1</f>
         <v>-0.184623898514324</v>
       </c>
-      <c r="J153" s="66" t="n">
+      <c r="J153" s="69" t="n">
         <f aca="false">+J149/F149-1</f>
         <v>-0.218170735780368</v>
       </c>
-      <c r="K153" s="66" t="n">
+      <c r="K153" s="69" t="n">
         <f aca="false">+K149/G149-1</f>
         <v>-0.125314655172414</v>
       </c>
-      <c r="L153" s="66" t="n">
+      <c r="L153" s="69" t="n">
         <f aca="false">+L149/H149-1</f>
         <v>0.0718694482513584</v>
       </c>
-      <c r="M153" s="66" t="n">
+      <c r="M153" s="69" t="n">
         <f aca="false">+M149/I149-1</f>
         <v>0.110787369562271</v>
       </c>
-      <c r="N153" s="66" t="n">
+      <c r="N153" s="69" t="n">
         <f aca="false">+N149/J149-1</f>
         <v>0.0665762671894103</v>
       </c>
-      <c r="O153" s="66" t="n">
+      <c r="O153" s="69" t="n">
         <f aca="false">+O149/K149-1</f>
         <v>-0.0217882932763541</v>
       </c>
-      <c r="P153" s="66" t="n">
+      <c r="P153" s="69" t="n">
         <f aca="false">+P149/L149-1</f>
         <v>-0.0987849779086898</v>
       </c>
-      <c r="Q153" s="66" t="n">
+      <c r="Q153" s="69" t="n">
         <f aca="false">+Q149/M149-1</f>
         <v>0.0651317964593778</v>
       </c>
-      <c r="R153" s="66" t="n">
+      <c r="R153" s="69" t="n">
         <f aca="false">+R149/N149-1</f>
         <v>0.154212818061985</v>
       </c>
-      <c r="S153" s="66" t="n">
+      <c r="S153" s="69" t="n">
         <f aca="false">+S149/O149-1</f>
         <v>0.208288102475033</v>
       </c>
-      <c r="AC153" s="66" t="n">
+      <c r="AC153" s="69" t="n">
         <f aca="false">+AC149/AB149-1</f>
         <v>-0.0239974944155282</v>
       </c>
-      <c r="AD153" s="66" t="n">
+      <c r="AD153" s="69" t="n">
         <f aca="false">+AD149/AC149-1</f>
         <v>-0.071821147085516</v>
       </c>
-      <c r="AE153" s="66" t="n">
+      <c r="AE153" s="69" t="n">
         <f aca="false">+AE149/AD149-1</f>
         <v>-0.0278682081369722</v>
       </c>
-      <c r="AF153" s="66" t="n">
+      <c r="AF153" s="69" t="n">
         <f aca="false">+AF149/AE149-1</f>
         <v>0.0754718201782312</v>
       </c>
-      <c r="AG153" s="66" t="n">
+      <c r="AG153" s="69" t="n">
         <f aca="false">+AG149/AF149-1</f>
         <v>0.0190727663983952</v>
       </c>
-      <c r="AH153" s="66" t="n">
+      <c r="AH153" s="69" t="n">
         <f aca="false">+AH149/AG149-1</f>
         <v>0.0187158042362394</v>
       </c>
-      <c r="AI153" s="66" t="n">
+      <c r="AI153" s="69" t="n">
         <f aca="false">+AI149/AH149-1</f>
         <v>0.0183719582619719</v>
       </c>
-      <c r="AJ153" s="66" t="n">
+      <c r="AJ153" s="69" t="n">
         <f aca="false">+AJ149/AI149-1</f>
         <v>0.018040518607098</v>
       </c>
-      <c r="AK153" s="66" t="n">
+      <c r="AK153" s="69" t="n">
         <f aca="false">+AK149/AJ149-1</f>
         <v>0.0177208257209462</v>
       </c>
-      <c r="AL153" s="66" t="n">
+      <c r="AL153" s="69" t="n">
         <f aca="false">+AL149/AK149-1</f>
         <v>0.0174122659899318</v>
       </c>
-      <c r="AM153" s="66" t="n">
+      <c r="AM153" s="69" t="n">
         <f aca="false">+AM149/AL149-1</f>
         <v>0.0171142678066594</v>
       </c>
-      <c r="AN153" s="66" t="n">
+      <c r="AN153" s="69" t="n">
         <f aca="false">+AN149/AM149-1</f>
         <v>0.0168262980358787</v>
       </c>
-      <c r="AO153" s="66" t="n">
+      <c r="AO153" s="69" t="n">
         <f aca="false">+AO149/AN149-1</f>
         <v>0.016547858831327</v>
       </c>
-      <c r="AP153" s="66" t="n">
+      <c r="AP153" s="69" t="n">
         <f aca="false">+AP149/AO149-1</f>
         <v>0.0162784847634732</v>
       </c>
-      <c r="AQ153" s="66" t="n">
+      <c r="AQ153" s="69" t="n">
         <f aca="false">+AQ149/AP149-1</f>
         <v>0.0160177402233028</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="X159" s="67"/>
-      <c r="Y159" s="67"/>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <f aca="false">+278-D157-C157-B157</f>
+        <v>278</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <f aca="false">+70-F157</f>
+        <v>1</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <f aca="false">+314-G157-F157</f>
+        <v>244</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <f aca="false">+314-H157-G157-F157</f>
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="K157" s="3" t="n">
+        <f aca="false">+97-J157</f>
+        <v>0</v>
+      </c>
+      <c r="L157" s="3" t="n">
+        <f aca="false">+361-K157-J157</f>
+        <v>264</v>
+      </c>
+      <c r="M157" s="3" t="n">
+        <f aca="false">+361-L157-K157-J157</f>
+        <v>0</v>
+      </c>
+      <c r="N157" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="O157" s="3" t="n">
+        <f aca="false">+96-N157</f>
+        <v>0</v>
+      </c>
+      <c r="P157" s="3" t="n">
+        <f aca="false">+348-O157-N157</f>
+        <v>252</v>
+      </c>
+      <c r="Q157" s="3" t="n">
+        <f aca="false">+348-P157-O157-N157</f>
+        <v>0</v>
+      </c>
+      <c r="R157" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="S157" s="3" t="n">
+        <f aca="false">+84-R157</f>
+        <v>0</v>
+      </c>
+      <c r="AA157" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB157" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="AC157" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="AD157" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="AE157" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="AF157" s="3" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="158" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E158" s="69" t="n">
+        <f aca="false">+E157/E$23</f>
+        <v>0.0614364640883978</v>
+      </c>
+      <c r="F158" s="69" t="n">
+        <f aca="false">+F157/F$23</f>
+        <v>0.0148227712137487</v>
+      </c>
+      <c r="G158" s="69" t="n">
+        <f aca="false">+G157/G$23</f>
+        <v>0.000207641196013289</v>
+      </c>
+      <c r="H158" s="69" t="n">
+        <f aca="false">+H157/H$23</f>
+        <v>0.0498977505112474</v>
+      </c>
+      <c r="I158" s="69" t="n">
+        <f aca="false">+I157/I$23</f>
+        <v>0</v>
+      </c>
+      <c r="J158" s="69" t="n">
+        <f aca="false">+J157/J$23</f>
+        <v>0.0187186414511772</v>
+      </c>
+      <c r="K158" s="69" t="n">
+        <f aca="false">+K157/K$23</f>
+        <v>0</v>
+      </c>
+      <c r="L158" s="69" t="n">
+        <f aca="false">+L157/L$23</f>
+        <v>0.0488165680473373</v>
+      </c>
+      <c r="M158" s="69" t="n">
+        <f aca="false">+M157/M$23</f>
+        <v>0</v>
+      </c>
+      <c r="N158" s="69" t="n">
+        <f aca="false">+N157/N$23</f>
+        <v>0.0168008400420021</v>
+      </c>
+      <c r="O158" s="69" t="n">
+        <f aca="false">+O157/O$23</f>
+        <v>0</v>
+      </c>
+      <c r="P158" s="69" t="n">
+        <f aca="false">+P157/P$23</f>
+        <v>0.0420841683366734</v>
+      </c>
+      <c r="Q158" s="69" t="n">
+        <f aca="false">+Q157/Q$23</f>
+        <v>0</v>
+      </c>
+      <c r="R158" s="69" t="n">
+        <f aca="false">+R157/R$23</f>
+        <v>0.013129102844639</v>
+      </c>
+      <c r="S158" s="69" t="n">
+        <f aca="false">+S157/S$23</f>
+        <v>0</v>
+      </c>
+      <c r="AA158" s="69" t="n">
+        <f aca="false">+AA157/AA$23</f>
+        <v>0.0209822816288468</v>
+      </c>
+      <c r="AB158" s="69" t="n">
+        <f aca="false">+AB157/AB$23</f>
+        <v>0.0184352233132721</v>
+      </c>
+      <c r="AC158" s="69" t="n">
+        <f aca="false">+AC157/AC$23</f>
+        <v>0.0157900715665114</v>
+      </c>
+      <c r="AD158" s="69" t="n">
+        <f aca="false">+AD157/AD$23</f>
+        <v>0.0161780617239425</v>
+      </c>
+      <c r="AE158" s="69" t="n">
+        <f aca="false">+AE157/AE$23</f>
+        <v>0.016786793768891</v>
+      </c>
+      <c r="AF158" s="69" t="n">
+        <f aca="false">+AF157/AF$23</f>
+        <v>0.0146409188438723</v>
+      </c>
+    </row>
+    <row r="159" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="I159" s="69" t="n">
+        <f aca="false">+I157/E157-1</f>
+        <v>-1</v>
+      </c>
+      <c r="J159" s="69" t="n">
+        <f aca="false">+J157/F157-1</f>
+        <v>0.405797101449275</v>
+      </c>
+      <c r="K159" s="69" t="n">
+        <f aca="false">+K157/G157-1</f>
+        <v>-1</v>
+      </c>
+      <c r="L159" s="69" t="n">
+        <f aca="false">+L157/H157-1</f>
+        <v>0.0819672131147542</v>
+      </c>
+      <c r="M159" s="69" t="e">
+        <f aca="false">+M157/I157-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N159" s="69" t="n">
+        <f aca="false">+N157/J157-1</f>
+        <v>-0.0103092783505154</v>
+      </c>
+      <c r="O159" s="69" t="e">
+        <f aca="false">+O157/K157-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P159" s="69" t="n">
+        <f aca="false">+P157/L157-1</f>
+        <v>-0.0454545454545454</v>
+      </c>
+      <c r="Q159" s="69" t="e">
+        <f aca="false">+Q157/M157-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R159" s="69" t="n">
+        <f aca="false">+R157/N157-1</f>
+        <v>-0.125</v>
+      </c>
+      <c r="S159" s="69" t="e">
+        <f aca="false">+S157/O157-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X159" s="70"/>
+      <c r="Y159" s="70"/>
+      <c r="AB159" s="69" t="n">
+        <f aca="false">+AB157/AA157-1</f>
+        <v>0.0777777777777777</v>
+      </c>
+      <c r="AC159" s="69" t="n">
+        <f aca="false">+AC157/AB157-1</f>
+        <v>-0.0446735395189003</v>
+      </c>
+      <c r="AD159" s="69" t="n">
+        <f aca="false">+AD157/AC157-1</f>
+        <v>0.129496402877698</v>
+      </c>
+      <c r="AE159" s="69" t="n">
+        <f aca="false">+AE157/AD157-1</f>
+        <v>0.14968152866242</v>
+      </c>
+      <c r="AF159" s="69" t="n">
+        <f aca="false">+AF157/AE157-1</f>
+        <v>-0.03601108033241</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <f aca="false">+6550-D160-C160-B160</f>
+        <v>6550</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <f aca="false">+2400-F160</f>
+        <v>1000</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <f aca="false">+3400-G160-F160</f>
+        <v>1000</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <f aca="false">+4400-H160-G160-F160</f>
+        <v>1000</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K160" s="3" t="n">
+        <f aca="false">+4500-J160</f>
+        <v>2500</v>
+      </c>
+      <c r="L160" s="3" t="n">
+        <f aca="false">+7000-K160-J160</f>
+        <v>2500</v>
+      </c>
+      <c r="M160" s="3" t="n">
+        <f aca="false">+9500-L160-K160-J160</f>
+        <v>2500</v>
+      </c>
+      <c r="N160" s="3" t="n">
+        <v>3250</v>
+      </c>
+      <c r="O160" s="3" t="n">
+        <f aca="false">+6750-N160</f>
+        <v>3500</v>
+      </c>
+      <c r="P160" s="3" t="n">
+        <f aca="false">+8807-O160-N160</f>
+        <v>2057</v>
+      </c>
+      <c r="Q160" s="3" t="n">
+        <f aca="false">+11281-P160-O160-N160</f>
+        <v>2474</v>
+      </c>
+      <c r="R160" s="3" t="n">
+        <v>2478</v>
+      </c>
+      <c r="S160" s="3" t="n">
+        <f aca="false">+4589-R160</f>
+        <v>2111</v>
+      </c>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
+      <c r="AA160" s="3" t="n">
+        <v>2050</v>
+      </c>
+      <c r="AB160" s="3" t="n">
+        <v>3950</v>
+      </c>
+      <c r="AC160" s="3" t="n">
+        <v>6550</v>
+      </c>
+      <c r="AD160" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="AE160" s="3" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AF160" s="3" t="n">
+        <v>11281</v>
+      </c>
     </row>
-    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T161" s="16"/>
-      <c r="U161" s="16"/>
-      <c r="V161" s="1"/>
-      <c r="W161" s="1"/>
-      <c r="X161" s="16"/>
-      <c r="Y161" s="16"/>
+    <row r="161" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E161" s="69" t="n">
+        <f aca="false">+E160/E$23</f>
+        <v>1.4475138121547</v>
+      </c>
+      <c r="F161" s="69" t="n">
+        <f aca="false">+F160/F$23</f>
+        <v>0.300751879699248</v>
+      </c>
+      <c r="G161" s="69" t="n">
+        <f aca="false">+G160/G$23</f>
+        <v>0.207641196013289</v>
+      </c>
+      <c r="H161" s="69" t="n">
+        <f aca="false">+H160/H$23</f>
+        <v>0.204498977505112</v>
+      </c>
+      <c r="I161" s="69" t="n">
+        <f aca="false">+I160/I$23</f>
+        <v>0.198098256735341</v>
+      </c>
+      <c r="J161" s="69" t="n">
+        <f aca="false">+J160/J$23</f>
+        <v>0.385951370127364</v>
+      </c>
+      <c r="K161" s="69" t="n">
+        <f aca="false">+K160/K$23</f>
+        <v>0.470898474288943</v>
+      </c>
+      <c r="L161" s="69" t="n">
+        <f aca="false">+L160/L$23</f>
+        <v>0.462278106508876</v>
+      </c>
+      <c r="M161" s="69" t="n">
+        <f aca="false">+M160/M$23</f>
+        <v>0.445950767035319</v>
+      </c>
+      <c r="N161" s="69" t="n">
+        <f aca="false">+N160/N$23</f>
+        <v>0.568778438921946</v>
+      </c>
+      <c r="O161" s="69" t="n">
+        <f aca="false">+O160/O$23</f>
+        <v>0.595947556615018</v>
+      </c>
+      <c r="P161" s="69" t="n">
+        <f aca="false">+P160/P$23</f>
+        <v>0.343520374081496</v>
+      </c>
+      <c r="Q161" s="69" t="n">
+        <f aca="false">+Q160/Q$23</f>
+        <v>0.399418792379722</v>
+      </c>
+      <c r="R161" s="69" t="n">
+        <f aca="false">+R160/R$23</f>
+        <v>0.387308533916849</v>
+      </c>
+      <c r="S161" s="69" t="n">
+        <f aca="false">+S160/S$23</f>
+        <v>0.318978543366576</v>
+      </c>
+      <c r="AA161" s="69" t="n">
+        <f aca="false">+AA160/AA$23</f>
+        <v>0.159309916070874</v>
+      </c>
+      <c r="AB161" s="69" t="n">
+        <f aca="false">+AB160/AB$23</f>
+        <v>0.250237567310738</v>
+      </c>
+      <c r="AC161" s="69" t="n">
+        <f aca="false">+AC160/AC$23</f>
+        <v>0.372032261728956</v>
+      </c>
+      <c r="AD161" s="69" t="n">
+        <f aca="false">+AD160/AD$23</f>
+        <v>0.226698954093462</v>
+      </c>
+      <c r="AE161" s="69" t="n">
+        <f aca="false">+AE160/AE$23</f>
+        <v>0.441757730760288</v>
+      </c>
+      <c r="AF161" s="69" t="n">
+        <f aca="false">+AF160/AF$23</f>
+        <v>0.474609785855526</v>
+      </c>
     </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="V162" s="1"/>
-      <c r="W162" s="1"/>
+    <row r="162" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="I162" s="69" t="n">
+        <f aca="false">+I160/E160-1</f>
+        <v>-0.847328244274809</v>
+      </c>
+      <c r="J162" s="69" t="n">
+        <f aca="false">+J160/F160-1</f>
+        <v>0.428571428571429</v>
+      </c>
+      <c r="K162" s="69" t="n">
+        <f aca="false">+K160/G160-1</f>
+        <v>1.5</v>
+      </c>
+      <c r="L162" s="69" t="n">
+        <f aca="false">+L160/H160-1</f>
+        <v>1.5</v>
+      </c>
+      <c r="M162" s="69" t="n">
+        <f aca="false">+M160/I160-1</f>
+        <v>1.5</v>
+      </c>
+      <c r="N162" s="69" t="n">
+        <f aca="false">+N160/J160-1</f>
+        <v>0.625</v>
+      </c>
+      <c r="O162" s="69" t="n">
+        <f aca="false">+O160/K160-1</f>
+        <v>0.4</v>
+      </c>
+      <c r="P162" s="69" t="n">
+        <f aca="false">+P160/L160-1</f>
+        <v>-0.1772</v>
+      </c>
+      <c r="Q162" s="69" t="n">
+        <f aca="false">+Q160/M160-1</f>
+        <v>-0.0104</v>
+      </c>
+      <c r="R162" s="69" t="n">
+        <f aca="false">+R160/N160-1</f>
+        <v>-0.237538461538462</v>
+      </c>
+      <c r="S162" s="69" t="n">
+        <f aca="false">+S160/O160-1</f>
+        <v>-0.396857142857143</v>
+      </c>
+      <c r="AB162" s="69" t="n">
+        <f aca="false">+AB160/AA160-1</f>
+        <v>0.926829268292683</v>
+      </c>
+      <c r="AC162" s="69" t="n">
+        <f aca="false">+AC160/AB160-1</f>
+        <v>0.658227848101266</v>
+      </c>
+      <c r="AD162" s="69" t="n">
+        <f aca="false">+AD160/AC160-1</f>
+        <v>-0.32824427480916</v>
+      </c>
+      <c r="AE162" s="69" t="n">
+        <f aca="false">+AE160/AD160-1</f>
+        <v>1.15909090909091</v>
+      </c>
+      <c r="AF162" s="69" t="n">
+        <f aca="false">+AF160/AE160-1</f>
+        <v>0.187473684210526</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="T163" s="16"/>
       <c r="U163" s="16"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
       <c r="X163" s="16"/>
       <c r="Y163" s="16"/>
+      <c r="AA163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T164" s="16"/>
-      <c r="U164" s="16"/>
-      <c r="V164" s="1"/>
-      <c r="W164" s="1"/>
-      <c r="X164" s="16"/>
-      <c r="Y164" s="16"/>
-      <c r="AR164" s="62"/>
-      <c r="AS164" s="62"/>
+    <row r="164" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E164" s="69" t="n">
+        <f aca="false">+E163/E$23</f>
+        <v>0</v>
+      </c>
+      <c r="F164" s="69" t="n">
+        <f aca="false">+F163/F$23</f>
+        <v>0</v>
+      </c>
+      <c r="G164" s="69" t="n">
+        <f aca="false">+G163/G$23</f>
+        <v>0</v>
+      </c>
+      <c r="H164" s="69" t="n">
+        <f aca="false">+H163/H$23</f>
+        <v>0</v>
+      </c>
+      <c r="I164" s="69" t="n">
+        <f aca="false">+I163/I$23</f>
+        <v>0</v>
+      </c>
+      <c r="J164" s="69" t="n">
+        <f aca="false">+J163/J$23</f>
+        <v>0</v>
+      </c>
+      <c r="K164" s="69" t="n">
+        <f aca="false">+K163/K$23</f>
+        <v>0</v>
+      </c>
+      <c r="L164" s="69" t="n">
+        <f aca="false">+L163/L$23</f>
+        <v>0</v>
+      </c>
+      <c r="M164" s="69" t="n">
+        <f aca="false">+M163/M$23</f>
+        <v>0</v>
+      </c>
+      <c r="N164" s="69" t="n">
+        <f aca="false">+N163/N$23</f>
+        <v>0</v>
+      </c>
+      <c r="O164" s="69" t="n">
+        <f aca="false">+O163/O$23</f>
+        <v>0</v>
+      </c>
+      <c r="P164" s="69" t="n">
+        <f aca="false">+P163/P$23</f>
+        <v>0</v>
+      </c>
+      <c r="Q164" s="69" t="n">
+        <f aca="false">+Q163/Q$23</f>
+        <v>0</v>
+      </c>
+      <c r="R164" s="69" t="n">
+        <f aca="false">+R163/R$23</f>
+        <v>0</v>
+      </c>
+      <c r="S164" s="69" t="n">
+        <f aca="false">+S163/S$23</f>
+        <v>0</v>
+      </c>
+      <c r="AA164" s="69" t="n">
+        <f aca="false">+AA163/AA$23</f>
+        <v>0</v>
+      </c>
+      <c r="AB164" s="69" t="n">
+        <f aca="false">+AB163/AB$23</f>
+        <v>0</v>
+      </c>
+      <c r="AC164" s="69" t="n">
+        <f aca="false">+AC163/AC$23</f>
+        <v>0</v>
+      </c>
+      <c r="AD164" s="69" t="n">
+        <f aca="false">+AD163/AD$23</f>
+        <v>0</v>
+      </c>
+      <c r="AE164" s="69" t="n">
+        <f aca="false">+AE163/AE$23</f>
+        <v>0</v>
+      </c>
+      <c r="AF164" s="69" t="n">
+        <f aca="false">+AF163/AF$23</f>
+        <v>0</v>
+      </c>
+      <c r="AR164" s="71"/>
+      <c r="AS164" s="71"/>
     </row>
-    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T165" s="16"/>
-      <c r="U165" s="16"/>
-      <c r="V165" s="1"/>
-      <c r="W165" s="1"/>
-      <c r="X165" s="16"/>
-      <c r="Y165" s="16"/>
-      <c r="AR165" s="61"/>
-      <c r="AS165" s="61"/>
+    <row r="165" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="I165" s="69" t="e">
+        <f aca="false">+I163/E163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J165" s="69" t="e">
+        <f aca="false">+J163/F163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K165" s="69" t="e">
+        <f aca="false">+K163/G163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L165" s="69" t="e">
+        <f aca="false">+L163/H163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M165" s="69" t="e">
+        <f aca="false">+M163/I163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N165" s="69" t="e">
+        <f aca="false">+N163/J163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O165" s="69" t="e">
+        <f aca="false">+O163/K163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P165" s="69" t="e">
+        <f aca="false">+P163/L163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q165" s="69" t="e">
+        <f aca="false">+Q163/M163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R165" s="69" t="e">
+        <f aca="false">+R163/N163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S165" s="69" t="e">
+        <f aca="false">+S163/O163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB165" s="69" t="e">
+        <f aca="false">+AB163/AA163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC165" s="69" t="e">
+        <f aca="false">+AC163/AB163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD165" s="69" t="e">
+        <f aca="false">+AD163/AC163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE165" s="69" t="e">
+        <f aca="false">+AE163/AD163-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF165" s="69" t="e">
+        <f aca="false">+AF163/AE163-1</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T166" s="16"/>
-      <c r="U166" s="16"/>
+      <c r="A166" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B166" s="3" t="n">
+        <f aca="false">+B160-B157+B163</f>
+        <v>0</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <f aca="false">+C160-C157+C163</f>
+        <v>0</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <f aca="false">+D160-D157+D163</f>
+        <v>0</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <f aca="false">+E160-E157+E163</f>
+        <v>6272</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <f aca="false">+F160-F157+F163</f>
+        <v>1331</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <f aca="false">+G160-G157+G163</f>
+        <v>999</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <f aca="false">+H160-H157+H163</f>
+        <v>756</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <f aca="false">+I160-I157+I163</f>
+        <v>1000</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <f aca="false">+J160-J157+J163</f>
+        <v>1903</v>
+      </c>
+      <c r="K166" s="3" t="n">
+        <f aca="false">+K160-K157+K163</f>
+        <v>2500</v>
+      </c>
+      <c r="L166" s="3" t="n">
+        <f aca="false">+L160-L157+L163</f>
+        <v>2236</v>
+      </c>
+      <c r="M166" s="3" t="n">
+        <f aca="false">+M160-M157+M163</f>
+        <v>2500</v>
+      </c>
+      <c r="N166" s="3" t="n">
+        <f aca="false">+N160-N157+N163</f>
+        <v>3154</v>
+      </c>
+      <c r="O166" s="3" t="n">
+        <f aca="false">+O160-O157+O163</f>
+        <v>3500</v>
+      </c>
+      <c r="P166" s="3" t="n">
+        <f aca="false">+P160-P157+P163</f>
+        <v>1805</v>
+      </c>
+      <c r="Q166" s="3" t="n">
+        <f aca="false">+Q160-Q157+Q163</f>
+        <v>2474</v>
+      </c>
+      <c r="R166" s="3" t="n">
+        <f aca="false">+R160-R157+R163</f>
+        <v>2394</v>
+      </c>
+      <c r="S166" s="3" t="n">
+        <f aca="false">+S160-S157+S163</f>
+        <v>2111</v>
+      </c>
+      <c r="T166" s="15" t="n">
+        <f aca="false">+T23*0.3</f>
+        <v>1994.004</v>
+      </c>
+      <c r="U166" s="15" t="n">
+        <f aca="false">+U23*0.3</f>
+        <v>2062.602</v>
+      </c>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
       <c r="X166" s="16"/>
       <c r="Y166" s="16"/>
-      <c r="AR166" s="61"/>
-      <c r="AS166" s="61"/>
+      <c r="AA166" s="3" t="n">
+        <f aca="false">+AA160-AA157+AA163</f>
+        <v>1780</v>
+      </c>
+      <c r="AB166" s="3" t="n">
+        <f aca="false">+AB160-AB157+AB163</f>
+        <v>3659</v>
+      </c>
+      <c r="AC166" s="3" t="n">
+        <f aca="false">+AC160-AC157+AC163</f>
+        <v>6272</v>
+      </c>
+      <c r="AD166" s="3" t="n">
+        <f aca="false">+AD160-AD157+AD163</f>
+        <v>4086</v>
+      </c>
+      <c r="AE166" s="3" t="n">
+        <f aca="false">+AE160-AE157+AE163</f>
+        <v>9139</v>
+      </c>
+      <c r="AF166" s="3" t="n">
+        <f aca="false">+AF160-AF157+AF163</f>
+        <v>10933</v>
+      </c>
+      <c r="AR166" s="62"/>
+      <c r="AS166" s="62"/>
     </row>
-    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T167" s="16"/>
-      <c r="U167" s="16"/>
-      <c r="V167" s="1"/>
-      <c r="W167" s="1"/>
-      <c r="X167" s="16"/>
-      <c r="Y167" s="16"/>
-      <c r="AR167" s="61"/>
-      <c r="AS167" s="61"/>
+    <row r="167" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E167" s="69" t="n">
+        <f aca="false">+E166/E$23</f>
+        <v>1.3860773480663</v>
+      </c>
+      <c r="F167" s="69" t="n">
+        <f aca="false">+F166/F$23</f>
+        <v>0.285929108485499</v>
+      </c>
+      <c r="G167" s="69" t="n">
+        <f aca="false">+G166/G$23</f>
+        <v>0.207433554817276</v>
+      </c>
+      <c r="H167" s="69" t="n">
+        <f aca="false">+H166/H$23</f>
+        <v>0.154601226993865</v>
+      </c>
+      <c r="I167" s="69" t="n">
+        <f aca="false">+I166/I$23</f>
+        <v>0.198098256735341</v>
+      </c>
+      <c r="J167" s="69" t="n">
+        <f aca="false">+J166/J$23</f>
+        <v>0.367232728676187</v>
+      </c>
+      <c r="K167" s="69" t="n">
+        <f aca="false">+K166/K$23</f>
+        <v>0.470898474288943</v>
+      </c>
+      <c r="L167" s="69" t="n">
+        <f aca="false">+L166/L$23</f>
+        <v>0.413461538461538</v>
+      </c>
+      <c r="M167" s="69" t="n">
+        <f aca="false">+M166/M$23</f>
+        <v>0.445950767035319</v>
+      </c>
+      <c r="N167" s="69" t="n">
+        <f aca="false">+N166/N$23</f>
+        <v>0.551977598879944</v>
+      </c>
+      <c r="O167" s="69" t="n">
+        <f aca="false">+O166/O$23</f>
+        <v>0.595947556615018</v>
+      </c>
+      <c r="P167" s="69" t="n">
+        <f aca="false">+P166/P$23</f>
+        <v>0.301436205744823</v>
+      </c>
+      <c r="Q167" s="69" t="n">
+        <f aca="false">+Q166/Q$23</f>
+        <v>0.399418792379722</v>
+      </c>
+      <c r="R167" s="69" t="n">
+        <f aca="false">+R166/R$23</f>
+        <v>0.37417943107221</v>
+      </c>
+      <c r="S167" s="69" t="n">
+        <f aca="false">+S166/S$23</f>
+        <v>0.318978543366576</v>
+      </c>
+      <c r="AA167" s="69" t="n">
+        <f aca="false">+AA166/AA$23</f>
+        <v>0.138327634442027</v>
+      </c>
+      <c r="AB167" s="69" t="n">
+        <f aca="false">+AB166/AB$23</f>
+        <v>0.231802343997466</v>
+      </c>
+      <c r="AC167" s="69" t="n">
+        <f aca="false">+AC166/AC$23</f>
+        <v>0.356242190162445</v>
+      </c>
+      <c r="AD167" s="69" t="n">
+        <f aca="false">+AD166/AD$23</f>
+        <v>0.210520892369519</v>
+      </c>
+      <c r="AE167" s="69" t="n">
+        <f aca="false">+AE166/AE$23</f>
+        <v>0.424970936991397</v>
+      </c>
+      <c r="AF167" s="69" t="n">
+        <f aca="false">+AF166/AF$23</f>
+        <v>0.459968867011654</v>
+      </c>
     </row>
-    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T168" s="16"/>
-      <c r="U168" s="16"/>
-      <c r="V168" s="1"/>
-      <c r="W168" s="1"/>
-      <c r="X168" s="16"/>
-      <c r="Y168" s="16"/>
-      <c r="AR168" s="61"/>
-      <c r="AS168" s="61"/>
+    <row r="168" s="69" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="I168" s="69" t="n">
+        <f aca="false">+I166/E166-1</f>
+        <v>-0.840561224489796</v>
+      </c>
+      <c r="J168" s="69" t="n">
+        <f aca="false">+J166/F166-1</f>
+        <v>0.429752066115702</v>
+      </c>
+      <c r="K168" s="69" t="n">
+        <f aca="false">+K166/G166-1</f>
+        <v>1.5025025025025</v>
+      </c>
+      <c r="L168" s="69" t="n">
+        <f aca="false">+L166/H166-1</f>
+        <v>1.95767195767196</v>
+      </c>
+      <c r="M168" s="69" t="n">
+        <f aca="false">+M166/I166-1</f>
+        <v>1.5</v>
+      </c>
+      <c r="N168" s="69" t="n">
+        <f aca="false">+N166/J166-1</f>
+        <v>0.657383079348397</v>
+      </c>
+      <c r="O168" s="69" t="n">
+        <f aca="false">+O166/K166-1</f>
+        <v>0.4</v>
+      </c>
+      <c r="P168" s="69" t="n">
+        <f aca="false">+P166/L166-1</f>
+        <v>-0.192754919499106</v>
+      </c>
+      <c r="Q168" s="69" t="n">
+        <f aca="false">+Q166/M166-1</f>
+        <v>-0.0104</v>
+      </c>
+      <c r="R168" s="69" t="n">
+        <f aca="false">+R166/N166-1</f>
+        <v>-0.240963855421687</v>
+      </c>
+      <c r="S168" s="69" t="n">
+        <f aca="false">+S166/O166-1</f>
+        <v>-0.396857142857143</v>
+      </c>
+      <c r="AB168" s="69" t="n">
+        <f aca="false">+AB166/AA166-1</f>
+        <v>1.05561797752809</v>
+      </c>
+      <c r="AC168" s="69" t="n">
+        <f aca="false">+AC166/AB166-1</f>
+        <v>0.714129543591145</v>
+      </c>
+      <c r="AD168" s="69" t="n">
+        <f aca="false">+AD166/AC166-1</f>
+        <v>-0.348533163265306</v>
+      </c>
+      <c r="AE168" s="69" t="n">
+        <f aca="false">+AE166/AD166-1</f>
+        <v>1.23666177190406</v>
+      </c>
+      <c r="AF168" s="69" t="n">
+        <f aca="false">+AF166/AE166-1</f>
+        <v>0.196301564722617</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="T169" s="16"/>
@@ -29124,8 +30161,8 @@
       <c r="W169" s="1"/>
       <c r="X169" s="16"/>
       <c r="Y169" s="16"/>
-      <c r="AR169" s="61"/>
-      <c r="AS169" s="61"/>
+      <c r="AR169" s="62"/>
+      <c r="AS169" s="62"/>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="T170" s="16"/>
@@ -29134,8 +30171,8 @@
       <c r="W170" s="1"/>
       <c r="X170" s="16"/>
       <c r="Y170" s="16"/>
-      <c r="AR170" s="61"/>
-      <c r="AS170" s="61"/>
+      <c r="AR170" s="62"/>
+      <c r="AS170" s="62"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="T171" s="16"/>
@@ -29144,8 +30181,8 @@
       <c r="W171" s="1"/>
       <c r="X171" s="16"/>
       <c r="Y171" s="16"/>
-      <c r="AR171" s="61"/>
-      <c r="AS171" s="61"/>
+      <c r="AR171" s="62"/>
+      <c r="AS171" s="62"/>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="T172" s="16"/>
@@ -29154,109 +30191,112 @@
       <c r="W172" s="1"/>
       <c r="X172" s="16"/>
       <c r="Y172" s="16"/>
-      <c r="AR172" s="61"/>
-      <c r="AS172" s="61"/>
+      <c r="AR172" s="62"/>
+      <c r="AS172" s="62"/>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
-      <c r="AR173" s="61"/>
-      <c r="AS173" s="61"/>
+      <c r="AR173" s="62"/>
+      <c r="AS173" s="62"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
-      <c r="AR174" s="61"/>
-      <c r="AS174" s="61"/>
+      <c r="AR174" s="62"/>
+      <c r="AS174" s="62"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AT175" s="62"/>
-      <c r="AU175" s="62"/>
-      <c r="AV175" s="62"/>
-      <c r="AW175" s="62"/>
-      <c r="AX175" s="62"/>
-      <c r="AY175" s="62"/>
-      <c r="AZ175" s="62"/>
-      <c r="BA175" s="62"/>
-      <c r="BB175" s="62"/>
-      <c r="BC175" s="62"/>
-      <c r="BD175" s="62"/>
-      <c r="BE175" s="62"/>
-      <c r="BF175" s="62"/>
-      <c r="BG175" s="62"/>
-      <c r="BH175" s="62"/>
-      <c r="BI175" s="62"/>
-      <c r="BJ175" s="62"/>
-      <c r="BK175" s="62"/>
-      <c r="BL175" s="62"/>
-      <c r="BM175" s="62"/>
-      <c r="BN175" s="62"/>
-      <c r="BO175" s="62"/>
-      <c r="BP175" s="62"/>
-      <c r="BQ175" s="62"/>
-      <c r="BR175" s="62"/>
-      <c r="BS175" s="62"/>
-      <c r="BT175" s="62"/>
-      <c r="BU175" s="62"/>
-      <c r="BV175" s="62"/>
-      <c r="BW175" s="62"/>
-      <c r="BX175" s="62"/>
-      <c r="BY175" s="62"/>
-      <c r="BZ175" s="62"/>
-      <c r="CA175" s="62"/>
-      <c r="CB175" s="62"/>
-      <c r="CC175" s="62"/>
-      <c r="CD175" s="62"/>
-      <c r="CE175" s="62"/>
-      <c r="CF175" s="62"/>
-      <c r="CG175" s="62"/>
-      <c r="CH175" s="62"/>
-      <c r="CI175" s="62"/>
-      <c r="CJ175" s="62"/>
-      <c r="CK175" s="62"/>
-      <c r="CL175" s="62"/>
-      <c r="CM175" s="62"/>
-      <c r="CN175" s="62"/>
-      <c r="CO175" s="62"/>
-      <c r="CP175" s="62"/>
-      <c r="CQ175" s="62"/>
-      <c r="CR175" s="62"/>
-      <c r="CS175" s="62"/>
-      <c r="CT175" s="62"/>
-      <c r="CU175" s="62"/>
-      <c r="CV175" s="62"/>
-      <c r="CW175" s="62"/>
-      <c r="CX175" s="62"/>
-      <c r="CY175" s="62"/>
-      <c r="CZ175" s="62"/>
-      <c r="DA175" s="62"/>
-      <c r="DB175" s="62"/>
-      <c r="DC175" s="62"/>
-      <c r="DD175" s="62"/>
-      <c r="DE175" s="62"/>
-      <c r="DF175" s="62"/>
-      <c r="DG175" s="62"/>
-      <c r="DH175" s="62"/>
-      <c r="DI175" s="62"/>
-      <c r="DJ175" s="62"/>
-      <c r="DK175" s="62"/>
-      <c r="DL175" s="62"/>
-      <c r="DM175" s="62"/>
-      <c r="DN175" s="62"/>
-      <c r="DO175" s="62"/>
-      <c r="DP175" s="62"/>
-      <c r="DQ175" s="62"/>
-      <c r="DR175" s="62"/>
-      <c r="DS175" s="62"/>
-      <c r="DT175" s="62"/>
-      <c r="DU175" s="62"/>
-      <c r="DV175" s="62"/>
-      <c r="DW175" s="62"/>
-      <c r="DX175" s="62"/>
-      <c r="DY175" s="62"/>
-      <c r="DZ175" s="62"/>
+      <c r="AT175" s="65"/>
+      <c r="AU175" s="65"/>
+      <c r="AV175" s="65"/>
+      <c r="AW175" s="65"/>
+      <c r="AX175" s="65"/>
+      <c r="AY175" s="65"/>
+      <c r="AZ175" s="65"/>
+      <c r="BA175" s="65"/>
+      <c r="BB175" s="65"/>
+      <c r="BC175" s="65"/>
+      <c r="BD175" s="65"/>
+      <c r="BE175" s="65"/>
+      <c r="BF175" s="65"/>
+      <c r="BG175" s="65"/>
+      <c r="BH175" s="65"/>
+      <c r="BI175" s="65"/>
+      <c r="BJ175" s="65"/>
+      <c r="BK175" s="65"/>
+      <c r="BL175" s="65"/>
+      <c r="BM175" s="65"/>
+      <c r="BN175" s="65"/>
+      <c r="BO175" s="65"/>
+      <c r="BP175" s="65"/>
+      <c r="BQ175" s="65"/>
+      <c r="BR175" s="65"/>
+      <c r="BS175" s="65"/>
+      <c r="BT175" s="65"/>
+      <c r="BU175" s="65"/>
+      <c r="BV175" s="65"/>
+      <c r="BW175" s="65"/>
+      <c r="BX175" s="65"/>
+      <c r="BY175" s="65"/>
+      <c r="BZ175" s="65"/>
+      <c r="CA175" s="65"/>
+      <c r="CB175" s="65"/>
+      <c r="CC175" s="65"/>
+      <c r="CD175" s="65"/>
+      <c r="CE175" s="65"/>
+      <c r="CF175" s="65"/>
+      <c r="CG175" s="65"/>
+      <c r="CH175" s="65"/>
+      <c r="CI175" s="65"/>
+      <c r="CJ175" s="65"/>
+      <c r="CK175" s="65"/>
+      <c r="CL175" s="65"/>
+      <c r="CM175" s="65"/>
+      <c r="CN175" s="65"/>
+      <c r="CO175" s="65"/>
+      <c r="CP175" s="65"/>
+      <c r="CQ175" s="65"/>
+      <c r="CR175" s="65"/>
+      <c r="CS175" s="65"/>
+      <c r="CT175" s="65"/>
+      <c r="CU175" s="65"/>
+      <c r="CV175" s="65"/>
+      <c r="CW175" s="65"/>
+      <c r="CX175" s="65"/>
+      <c r="CY175" s="65"/>
+      <c r="CZ175" s="65"/>
+      <c r="DA175" s="65"/>
+      <c r="DB175" s="65"/>
+      <c r="DC175" s="65"/>
+      <c r="DD175" s="65"/>
+      <c r="DE175" s="65"/>
+      <c r="DF175" s="65"/>
+      <c r="DG175" s="65"/>
+      <c r="DH175" s="65"/>
+      <c r="DI175" s="65"/>
+      <c r="DJ175" s="65"/>
+      <c r="DK175" s="65"/>
+      <c r="DL175" s="65"/>
+      <c r="DM175" s="65"/>
+      <c r="DN175" s="65"/>
+      <c r="DO175" s="65"/>
+      <c r="DP175" s="65"/>
+      <c r="DQ175" s="65"/>
+      <c r="DR175" s="65"/>
+      <c r="DS175" s="65"/>
+      <c r="DT175" s="65"/>
+      <c r="DU175" s="65"/>
+      <c r="DV175" s="65"/>
+      <c r="DW175" s="65"/>
+      <c r="DX175" s="65"/>
+      <c r="DY175" s="65"/>
+      <c r="DZ175" s="65"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="AW63:AX63"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId2" location="Main" display="Main"/>
   </hyperlinks>
@@ -29290,19 +30330,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="72" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="32" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E3" s="32"/>
       <c r="F3" s="32"/>
@@ -29310,13 +30350,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="32" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C4" s="32" t="n">
         <v>2.15</v>
       </c>
-      <c r="D4" s="69" t="s">
-        <v>251</v>
+      <c r="D4" s="73" t="s">
+        <v>265</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
@@ -29324,13 +30364,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C5" s="32" t="n">
         <v>4.85</v>
       </c>
-      <c r="D5" s="69" t="s">
-        <v>253</v>
+      <c r="D5" s="73" t="s">
+        <v>267</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
@@ -29338,13 +30378,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="32" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C6" s="32" t="n">
         <v>4.75</v>
       </c>
-      <c r="D6" s="69" t="s">
-        <v>255</v>
+      <c r="D6" s="73" t="s">
+        <v>269</v>
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="32"/>
@@ -29352,13 +30392,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="32" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C7" s="32" t="n">
         <v>4.8</v>
       </c>
-      <c r="D7" s="69" t="s">
-        <v>257</v>
+      <c r="D7" s="73" t="s">
+        <v>271</v>
       </c>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
@@ -29366,13 +30406,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="32" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C8" s="32" t="n">
         <v>4.95</v>
       </c>
-      <c r="D8" s="69" t="s">
-        <v>259</v>
+      <c r="D8" s="73" t="s">
+        <v>273</v>
       </c>
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
@@ -29380,13 +30420,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="32" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C9" s="32" t="n">
         <v>2.3</v>
       </c>
-      <c r="D9" s="69" t="s">
-        <v>261</v>
+      <c r="D9" s="73" t="s">
+        <v>275</v>
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
@@ -29394,13 +30434,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="32" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C10" s="32" t="n">
         <v>4.95</v>
       </c>
-      <c r="D10" s="69" t="s">
-        <v>263</v>
+      <c r="D10" s="73" t="s">
+        <v>277</v>
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
@@ -29408,20 +30448,20 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="32" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C11" s="32" t="n">
         <v>5.3</v>
       </c>
-      <c r="D11" s="69" t="s">
-        <v>265</v>
+      <c r="D11" s="73" t="s">
+        <v>279</v>
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="70" t="n">
+      <c r="C12" s="74" t="n">
         <f aca="false">+AVERAGE(C4:C11)</f>
         <v>4.25625</v>
       </c>
@@ -29453,14 +30493,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="72" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
